--- a/JSON_Data/static/22级技能效果.xlsx
+++ b/JSON_Data/static/22级技能效果.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSCodeproject\Vue\世界OL\attribute\public\static\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732FFE97-D765-406A-A979-12F1EF5B8DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3983" uniqueCount="1626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3983" uniqueCount="1627">
   <si>
     <t>技能名称</t>
   </si>
@@ -4892,18 +4898,21 @@
   </si>
   <si>
     <t>法力+1000,不死意志</t>
+  </si>
+  <si>
+    <t>主动技能</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4946,9 +4955,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF92d050"/>
+      <color rgb="FF92D050"/>
       <name val="微软雅黑"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5007,61 +5023,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -5072,10 +5091,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -5113,71 +5132,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -5205,7 +5224,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -5228,11 +5247,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -5241,13 +5260,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -5257,7 +5276,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -5266,7 +5285,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -5275,7 +5294,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -5283,10 +5302,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -5351,30 +5370,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N504"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N503"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="14" width="24.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="14" width="11.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="14" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="15" width="11.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="14" width="47.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="14" width="41.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="14" width="31.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="14" width="14.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="14" width="15.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="14" width="13.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="14" width="31.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="14" width="21.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="24.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.6640625" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21">
+    <row r="1" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5418,7 +5436,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21">
+    <row r="2" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
@@ -5458,7 +5476,7 @@
       </c>
       <c r="N2" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21">
+    <row r="3" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>24</v>
       </c>
@@ -5498,7 +5516,7 @@
       </c>
       <c r="N3" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21">
+    <row r="4" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>31</v>
       </c>
@@ -5538,7 +5556,7 @@
       </c>
       <c r="N4" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21">
+    <row r="5" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>34</v>
       </c>
@@ -5578,7 +5596,7 @@
       </c>
       <c r="N5" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21">
+    <row r="6" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>39</v>
       </c>
@@ -5620,7 +5638,7 @@
       </c>
       <c r="N6" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21">
+    <row r="7" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>44</v>
       </c>
@@ -5658,7 +5676,7 @@
       </c>
       <c r="N7" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21">
+    <row r="8" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>49</v>
       </c>
@@ -5698,7 +5716,7 @@
       </c>
       <c r="N8" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21">
+    <row r="9" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>54</v>
       </c>
@@ -5738,7 +5756,7 @@
       </c>
       <c r="N9" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21">
+    <row r="10" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>56</v>
       </c>
@@ -5776,7 +5794,7 @@
       </c>
       <c r="N10" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21">
+    <row r="11" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>59</v>
       </c>
@@ -5816,7 +5834,7 @@
       </c>
       <c r="N11" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21">
+    <row r="12" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>65</v>
       </c>
@@ -5856,7 +5874,7 @@
       </c>
       <c r="N12" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="21">
+    <row r="13" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>70</v>
       </c>
@@ -5894,7 +5912,7 @@
       </c>
       <c r="N13" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="21">
+    <row r="14" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>76</v>
       </c>
@@ -5936,7 +5954,7 @@
       </c>
       <c r="N14" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21">
+    <row r="15" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>81</v>
       </c>
@@ -5976,7 +5994,7 @@
       </c>
       <c r="N15" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21">
+    <row r="16" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>84</v>
       </c>
@@ -6018,7 +6036,7 @@
       </c>
       <c r="N16" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="21">
+    <row r="17" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>87</v>
       </c>
@@ -6058,7 +6076,7 @@
       </c>
       <c r="N17" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="21">
+    <row r="18" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>90</v>
       </c>
@@ -6098,7 +6116,7 @@
       </c>
       <c r="N18" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="21">
+    <row r="19" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>95</v>
       </c>
@@ -6140,7 +6158,7 @@
       </c>
       <c r="N19" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>100</v>
       </c>
@@ -6180,7 +6198,7 @@
       </c>
       <c r="N20" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>104</v>
       </c>
@@ -6218,7 +6236,7 @@
       </c>
       <c r="N21" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>107</v>
       </c>
@@ -6254,7 +6272,7 @@
       </c>
       <c r="N22" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>111</v>
       </c>
@@ -6296,7 +6314,7 @@
       </c>
       <c r="N23" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>115</v>
       </c>
@@ -6336,7 +6354,7 @@
       </c>
       <c r="N24" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>119</v>
       </c>
@@ -6376,7 +6394,7 @@
       </c>
       <c r="N25" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>124</v>
       </c>
@@ -6416,7 +6434,7 @@
       </c>
       <c r="N26" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row r="27" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>128</v>
       </c>
@@ -6458,7 +6476,7 @@
       </c>
       <c r="N27" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>132</v>
       </c>
@@ -6496,7 +6514,7 @@
       </c>
       <c r="N28" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row r="29" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>136</v>
       </c>
@@ -6532,7 +6550,7 @@
       </c>
       <c r="N29" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>138</v>
       </c>
@@ -6574,7 +6592,7 @@
       </c>
       <c r="N30" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row r="31" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>143</v>
       </c>
@@ -6618,7 +6636,7 @@
         <v>147</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>148</v>
       </c>
@@ -6662,7 +6680,7 @@
         <v>153</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row r="33" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -6678,7 +6696,7 @@
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>154</v>
       </c>
@@ -6708,7 +6726,7 @@
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row r="35" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>159</v>
       </c>
@@ -6738,7 +6756,7 @@
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>163</v>
       </c>
@@ -6768,7 +6786,7 @@
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>166</v>
       </c>
@@ -6796,7 +6814,7 @@
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>169</v>
       </c>
@@ -6826,7 +6844,7 @@
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>173</v>
       </c>
@@ -6854,7 +6872,7 @@
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>176</v>
       </c>
@@ -6882,7 +6900,7 @@
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>179</v>
       </c>
@@ -6912,7 +6930,7 @@
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>183</v>
       </c>
@@ -6940,7 +6958,7 @@
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row r="43" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>186</v>
       </c>
@@ -6970,7 +6988,7 @@
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>190</v>
       </c>
@@ -7000,7 +7018,7 @@
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row r="45" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>192</v>
       </c>
@@ -7030,7 +7048,7 @@
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row r="46" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>24</v>
       </c>
@@ -7060,7 +7078,7 @@
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row r="47" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>198</v>
       </c>
@@ -7090,7 +7108,7 @@
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row r="48" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>201</v>
       </c>
@@ -7120,7 +7138,7 @@
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+    <row r="49" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>205</v>
       </c>
@@ -7150,7 +7168,7 @@
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+    <row r="50" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>207</v>
       </c>
@@ -7178,7 +7196,7 @@
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
+    <row r="51" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>210</v>
       </c>
@@ -7208,7 +7226,7 @@
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+    <row r="52" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>214</v>
       </c>
@@ -7236,7 +7254,7 @@
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
+    <row r="53" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>216</v>
       </c>
@@ -7268,7 +7286,7 @@
         <v>147</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+    <row r="54" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>220</v>
       </c>
@@ -7300,7 +7318,7 @@
         <v>153</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
+    <row r="55" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>224</v>
       </c>
@@ -7332,7 +7350,7 @@
         <v>147</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
+    <row r="56" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>227</v>
       </c>
@@ -7364,7 +7382,7 @@
         <v>147</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
+    <row r="57" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -7380,7 +7398,7 @@
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
+    <row r="58" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>231</v>
       </c>
@@ -7420,7 +7438,7 @@
       </c>
       <c r="N58" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
+    <row r="59" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>238</v>
       </c>
@@ -7458,7 +7476,7 @@
       </c>
       <c r="N59" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+    <row r="60" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>241</v>
       </c>
@@ -7496,7 +7514,7 @@
       </c>
       <c r="N60" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+    <row r="61" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>245</v>
       </c>
@@ -7536,7 +7554,7 @@
       </c>
       <c r="N61" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
+    <row r="62" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>249</v>
       </c>
@@ -7574,7 +7592,7 @@
       </c>
       <c r="N62" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
+    <row r="63" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>252</v>
       </c>
@@ -7612,7 +7630,7 @@
       </c>
       <c r="N63" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+    <row r="64" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>256</v>
       </c>
@@ -7650,7 +7668,7 @@
       </c>
       <c r="N64" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+    <row r="65" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>259</v>
       </c>
@@ -7690,7 +7708,7 @@
       </c>
       <c r="N65" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+    <row r="66" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>263</v>
       </c>
@@ -7728,7 +7746,7 @@
       </c>
       <c r="N66" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+    <row r="67" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>267</v>
       </c>
@@ -7768,7 +7786,7 @@
       </c>
       <c r="N67" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+    <row r="68" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>271</v>
       </c>
@@ -7806,7 +7824,7 @@
       </c>
       <c r="N68" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
+    <row r="69" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>275</v>
       </c>
@@ -7846,7 +7864,7 @@
       </c>
       <c r="N69" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
+    <row r="70" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>278</v>
       </c>
@@ -7886,7 +7904,7 @@
       </c>
       <c r="N70" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+    <row r="71" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>281</v>
       </c>
@@ -7924,7 +7942,7 @@
       </c>
       <c r="N71" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+    <row r="72" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>285</v>
       </c>
@@ -7968,7 +7986,7 @@
         <v>147</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+    <row r="73" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>290</v>
       </c>
@@ -8010,7 +8028,7 @@
         <v>147</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+    <row r="74" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>294</v>
       </c>
@@ -8052,7 +8070,7 @@
         <v>153</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+    <row r="75" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>298</v>
       </c>
@@ -8094,7 +8112,7 @@
         <v>153</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+    <row r="76" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -8110,7 +8128,7 @@
       <c r="M76" s="4"/>
       <c r="N76" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+    <row r="77" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>303</v>
       </c>
@@ -8150,7 +8168,7 @@
       </c>
       <c r="N77" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+    <row r="78" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>309</v>
       </c>
@@ -8190,7 +8208,7 @@
       </c>
       <c r="N78" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+    <row r="79" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>314</v>
       </c>
@@ -8230,7 +8248,7 @@
       </c>
       <c r="N79" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+    <row r="80" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>318</v>
       </c>
@@ -8270,7 +8288,7 @@
       </c>
       <c r="N80" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+    <row r="81" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>322</v>
       </c>
@@ -8308,7 +8326,7 @@
       </c>
       <c r="N81" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+    <row r="82" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>327</v>
       </c>
@@ -8346,7 +8364,7 @@
       </c>
       <c r="N82" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
+    <row r="83" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>332</v>
       </c>
@@ -8384,7 +8402,7 @@
       </c>
       <c r="N83" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
+    <row r="84" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>336</v>
       </c>
@@ -8422,7 +8440,7 @@
       </c>
       <c r="N84" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
+    <row r="85" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>340</v>
       </c>
@@ -8458,7 +8476,7 @@
       </c>
       <c r="N85" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
+    <row r="86" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>342</v>
       </c>
@@ -8498,7 +8516,7 @@
       </c>
       <c r="N86" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
+    <row r="87" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>346</v>
       </c>
@@ -8538,7 +8556,7 @@
       </c>
       <c r="N87" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
+    <row r="88" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>353</v>
       </c>
@@ -8578,7 +8596,7 @@
       </c>
       <c r="N88" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
+    <row r="89" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>357</v>
       </c>
@@ -8616,7 +8634,7 @@
       </c>
       <c r="N89" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
+    <row r="90" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>359</v>
       </c>
@@ -8656,7 +8674,7 @@
       </c>
       <c r="N90" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
+    <row r="91" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>362</v>
       </c>
@@ -8694,7 +8712,7 @@
       </c>
       <c r="N91" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
+    <row r="92" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>367</v>
       </c>
@@ -8736,7 +8754,7 @@
       </c>
       <c r="N92" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+    <row r="93" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>370</v>
       </c>
@@ -8776,7 +8794,7 @@
       </c>
       <c r="N93" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+    <row r="94" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>374</v>
       </c>
@@ -8814,7 +8832,7 @@
       </c>
       <c r="N94" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
+    <row r="95" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>379</v>
       </c>
@@ -8854,7 +8872,7 @@
       </c>
       <c r="N95" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
+    <row r="96" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>383</v>
       </c>
@@ -8892,7 +8910,7 @@
       </c>
       <c r="N96" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
+    <row r="97" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>387</v>
       </c>
@@ -8930,7 +8948,7 @@
       </c>
       <c r="N97" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
+    <row r="98" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>390</v>
       </c>
@@ -8970,7 +8988,7 @@
       </c>
       <c r="N98" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
+    <row r="99" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>393</v>
       </c>
@@ -9012,7 +9030,7 @@
         <v>398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
+    <row r="100" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>399</v>
       </c>
@@ -9054,7 +9072,7 @@
         <v>398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
+    <row r="101" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>402</v>
       </c>
@@ -9096,7 +9114,7 @@
         <v>398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
+    <row r="102" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>407</v>
       </c>
@@ -9138,7 +9156,7 @@
         <v>398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
+    <row r="103" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -9154,7 +9172,7 @@
       <c r="M103" s="4"/>
       <c r="N103" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
+    <row r="104" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
         <v>409</v>
       </c>
@@ -9184,7 +9202,7 @@
       <c r="M104" s="4"/>
       <c r="N104" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
+    <row r="105" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>413</v>
       </c>
@@ -9212,7 +9230,7 @@
       <c r="M105" s="4"/>
       <c r="N105" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
+    <row r="106" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
         <v>416</v>
       </c>
@@ -9240,7 +9258,7 @@
       <c r="M106" s="4"/>
       <c r="N106" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
+    <row r="107" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>419</v>
       </c>
@@ -9268,7 +9286,7 @@
       <c r="M107" s="4"/>
       <c r="N107" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
+    <row r="108" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
         <v>421</v>
       </c>
@@ -9296,7 +9314,7 @@
       <c r="M108" s="4"/>
       <c r="N108" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
+    <row r="109" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
         <v>424</v>
       </c>
@@ -9326,7 +9344,7 @@
       <c r="M109" s="4"/>
       <c r="N109" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
+    <row r="110" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
         <v>428</v>
       </c>
@@ -9354,7 +9372,7 @@
       <c r="M110" s="4"/>
       <c r="N110" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
+    <row r="111" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>431</v>
       </c>
@@ -9382,7 +9400,7 @@
       <c r="M111" s="4"/>
       <c r="N111" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
+    <row r="112" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
         <v>433</v>
       </c>
@@ -9412,7 +9430,7 @@
       <c r="M112" s="4"/>
       <c r="N112" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
+    <row r="113" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>437</v>
       </c>
@@ -9440,7 +9458,7 @@
       <c r="M113" s="4"/>
       <c r="N113" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
+    <row r="114" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
         <v>440</v>
       </c>
@@ -9468,7 +9486,7 @@
       <c r="M114" s="4"/>
       <c r="N114" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
+    <row r="115" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>443</v>
       </c>
@@ -9496,7 +9514,7 @@
       <c r="M115" s="4"/>
       <c r="N115" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
+    <row r="116" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
         <v>446</v>
       </c>
@@ -9526,7 +9544,7 @@
       <c r="M116" s="4"/>
       <c r="N116" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
+    <row r="117" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>449</v>
       </c>
@@ -9556,7 +9574,7 @@
       <c r="M117" s="4"/>
       <c r="N117" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
+    <row r="118" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
         <v>452</v>
       </c>
@@ -9584,7 +9602,7 @@
       <c r="M118" s="4"/>
       <c r="N118" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
+    <row r="119" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>455</v>
       </c>
@@ -9614,7 +9632,7 @@
       <c r="M119" s="4"/>
       <c r="N119" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
+    <row r="120" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
         <v>459</v>
       </c>
@@ -9642,7 +9660,7 @@
       <c r="M120" s="4"/>
       <c r="N120" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
+    <row r="121" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>462</v>
       </c>
@@ -9670,7 +9688,7 @@
       <c r="M121" s="4"/>
       <c r="N121" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
+    <row r="122" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
         <v>464</v>
       </c>
@@ -9702,7 +9720,7 @@
         <v>398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
+    <row r="123" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
         <v>468</v>
       </c>
@@ -9732,7 +9750,7 @@
         <v>398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
+    <row r="124" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
         <v>471</v>
       </c>
@@ -9764,7 +9782,7 @@
         <v>398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
+    <row r="125" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
         <v>475</v>
       </c>
@@ -9796,7 +9814,7 @@
         <v>398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
+    <row r="126" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
         <v>479</v>
       </c>
@@ -9828,7 +9846,7 @@
         <v>480</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
+    <row r="127" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
         <v>481</v>
       </c>
@@ -9858,7 +9876,7 @@
         <v>480</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
+    <row r="128" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
         <v>483</v>
       </c>
@@ -9888,7 +9906,7 @@
         <v>480</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
+    <row r="129" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
         <v>485</v>
       </c>
@@ -9918,7 +9936,7 @@
       <c r="M129" s="4"/>
       <c r="N129" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
+    <row r="130" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
         <v>489</v>
       </c>
@@ -9950,7 +9968,7 @@
         <v>480</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
+    <row r="131" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -9966,7 +9984,7 @@
       <c r="M131" s="4"/>
       <c r="N131" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
+    <row r="132" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
         <v>493</v>
       </c>
@@ -10006,7 +10024,7 @@
       </c>
       <c r="N132" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
+    <row r="133" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
         <v>498</v>
       </c>
@@ -10044,7 +10062,7 @@
       </c>
       <c r="N133" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
+    <row r="134" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
         <v>501</v>
       </c>
@@ -10084,7 +10102,7 @@
       </c>
       <c r="N134" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
+    <row r="135" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
         <v>505</v>
       </c>
@@ -10124,7 +10142,7 @@
       </c>
       <c r="N135" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
+    <row r="136" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
         <v>509</v>
       </c>
@@ -10162,7 +10180,7 @@
       </c>
       <c r="N136" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
+    <row r="137" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
         <v>512</v>
       </c>
@@ -10202,7 +10220,7 @@
       </c>
       <c r="N137" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
+    <row r="138" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
         <v>515</v>
       </c>
@@ -10242,7 +10260,7 @@
       </c>
       <c r="N138" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
+    <row r="139" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
         <v>519</v>
       </c>
@@ -10282,7 +10300,7 @@
       </c>
       <c r="N139" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
+    <row r="140" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
         <v>523</v>
       </c>
@@ -10320,7 +10338,7 @@
       </c>
       <c r="N140" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
+    <row r="141" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>527</v>
       </c>
@@ -10362,7 +10380,7 @@
         <v>398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
+    <row r="142" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -10378,7 +10396,7 @@
       <c r="M142" s="4"/>
       <c r="N142" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
+    <row r="143" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>532</v>
       </c>
@@ -10414,7 +10432,7 @@
       </c>
       <c r="N143" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
+    <row r="144" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
         <v>536</v>
       </c>
@@ -10454,7 +10472,7 @@
       </c>
       <c r="N144" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
+    <row r="145" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
         <v>541</v>
       </c>
@@ -10494,7 +10512,7 @@
       </c>
       <c r="N145" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
+    <row r="146" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
         <v>546</v>
       </c>
@@ -10532,7 +10550,7 @@
       </c>
       <c r="N146" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
+    <row r="147" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>552</v>
       </c>
@@ -10570,7 +10588,7 @@
       </c>
       <c r="N147" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
+    <row r="148" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>557</v>
       </c>
@@ -10610,7 +10628,7 @@
       </c>
       <c r="N148" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
+    <row r="149" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>561</v>
       </c>
@@ -10650,7 +10668,7 @@
       </c>
       <c r="N149" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
+    <row r="150" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>566</v>
       </c>
@@ -10690,7 +10708,7 @@
       </c>
       <c r="N150" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
+    <row r="151" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>570</v>
       </c>
@@ -10728,7 +10746,7 @@
       </c>
       <c r="N151" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75">
+    <row r="152" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
         <v>573</v>
       </c>
@@ -10766,7 +10784,7 @@
       </c>
       <c r="N152" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
+    <row r="153" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>575</v>
       </c>
@@ -10804,7 +10822,7 @@
       </c>
       <c r="N153" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
+    <row r="154" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
         <v>578</v>
       </c>
@@ -10844,7 +10862,7 @@
       </c>
       <c r="N154" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
+    <row r="155" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
         <v>582</v>
       </c>
@@ -10884,7 +10902,7 @@
       </c>
       <c r="N155" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
+    <row r="156" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
         <v>584</v>
       </c>
@@ -10924,7 +10942,7 @@
       </c>
       <c r="N156" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
+    <row r="157" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>586</v>
       </c>
@@ -10964,7 +10982,7 @@
       </c>
       <c r="N157" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
+    <row r="158" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
         <v>591</v>
       </c>
@@ -11006,7 +11024,7 @@
       </c>
       <c r="N158" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
+    <row r="159" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
         <v>595</v>
       </c>
@@ -11046,7 +11064,7 @@
       </c>
       <c r="N159" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
+    <row r="160" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
         <v>599</v>
       </c>
@@ -11088,7 +11106,7 @@
       </c>
       <c r="N160" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
+    <row r="161" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
         <v>603</v>
       </c>
@@ -11128,7 +11146,7 @@
       </c>
       <c r="N161" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
+    <row r="162" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>605</v>
       </c>
@@ -11170,7 +11188,7 @@
       </c>
       <c r="N162" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
+    <row r="163" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>608</v>
       </c>
@@ -11212,7 +11230,7 @@
       </c>
       <c r="N163" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
+    <row r="164" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>612</v>
       </c>
@@ -11252,7 +11270,7 @@
       </c>
       <c r="N164" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
+    <row r="165" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>615</v>
       </c>
@@ -11292,7 +11310,7 @@
       </c>
       <c r="N165" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
+    <row r="166" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
         <v>617</v>
       </c>
@@ -11332,7 +11350,7 @@
       </c>
       <c r="N166" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
+    <row r="167" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
         <v>620</v>
       </c>
@@ -11372,7 +11390,7 @@
       </c>
       <c r="N167" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
+    <row r="168" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
         <v>625</v>
       </c>
@@ -11410,7 +11428,7 @@
       </c>
       <c r="N168" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75">
+    <row r="169" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
         <v>628</v>
       </c>
@@ -11454,7 +11472,7 @@
         <v>632</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75">
+    <row r="170" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
         <v>633</v>
       </c>
@@ -11496,7 +11514,7 @@
         <v>632</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75">
+    <row r="171" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
         <v>637</v>
       </c>
@@ -11538,7 +11556,7 @@
         <v>641</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75">
+    <row r="172" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
         <v>642</v>
       </c>
@@ -11580,7 +11598,7 @@
         <v>641</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75">
+    <row r="173" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
         <v>645</v>
       </c>
@@ -11622,7 +11640,7 @@
         <v>641</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75">
+    <row r="174" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
         <v>649</v>
       </c>
@@ -11666,7 +11684,7 @@
         <v>641</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75">
+    <row r="175" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -11682,7 +11700,7 @@
       <c r="M175" s="4"/>
       <c r="N175" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="18.75">
+    <row r="176" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
         <v>654</v>
       </c>
@@ -11712,7 +11730,7 @@
       <c r="M176" s="4"/>
       <c r="N176" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="18.75">
+    <row r="177" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
         <v>658</v>
       </c>
@@ -11742,7 +11760,7 @@
       <c r="M177" s="4"/>
       <c r="N177" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="18.75">
+    <row r="178" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
         <v>661</v>
       </c>
@@ -11770,7 +11788,7 @@
       <c r="M178" s="4"/>
       <c r="N178" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="18.75">
+    <row r="179" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
         <v>664</v>
       </c>
@@ -11798,7 +11816,7 @@
       <c r="M179" s="4"/>
       <c r="N179" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="18.75">
+    <row r="180" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
         <v>667</v>
       </c>
@@ -11828,7 +11846,7 @@
       <c r="M180" s="4"/>
       <c r="N180" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="18.75">
+    <row r="181" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
         <v>669</v>
       </c>
@@ -11856,7 +11874,7 @@
       <c r="M181" s="4"/>
       <c r="N181" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="18.75">
+    <row r="182" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
         <v>672</v>
       </c>
@@ -11886,7 +11904,7 @@
       <c r="M182" s="4"/>
       <c r="N182" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18.75">
+    <row r="183" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
         <v>674</v>
       </c>
@@ -11914,7 +11932,7 @@
       <c r="M183" s="4"/>
       <c r="N183" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="21">
+    <row r="184" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
         <v>677</v>
       </c>
@@ -11944,7 +11962,7 @@
       <c r="M184" s="4"/>
       <c r="N184" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="21">
+    <row r="185" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
         <v>681</v>
       </c>
@@ -11972,7 +11990,7 @@
       <c r="M185" s="4"/>
       <c r="N185" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="21">
+    <row r="186" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
         <v>684</v>
       </c>
@@ -12000,7 +12018,7 @@
       <c r="M186" s="4"/>
       <c r="N186" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="21">
+    <row r="187" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
         <v>687</v>
       </c>
@@ -12028,7 +12046,7 @@
       <c r="M187" s="4"/>
       <c r="N187" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="21">
+    <row r="188" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
         <v>688</v>
       </c>
@@ -12056,7 +12074,7 @@
       <c r="M188" s="4"/>
       <c r="N188" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="21">
+    <row r="189" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
         <v>691</v>
       </c>
@@ -12084,7 +12102,7 @@
       <c r="M189" s="4"/>
       <c r="N189" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="21">
+    <row r="190" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
         <v>694</v>
       </c>
@@ -12114,7 +12132,7 @@
       <c r="M190" s="4"/>
       <c r="N190" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="21">
+    <row r="191" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
         <v>698</v>
       </c>
@@ -12142,7 +12160,7 @@
       <c r="M191" s="4"/>
       <c r="N191" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="21">
+    <row r="192" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
         <v>701</v>
       </c>
@@ -12172,7 +12190,7 @@
       <c r="M192" s="4"/>
       <c r="N192" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="21">
+    <row r="193" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
         <v>705</v>
       </c>
@@ -12200,7 +12218,7 @@
       <c r="M193" s="4"/>
       <c r="N193" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="21">
+    <row r="194" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
         <v>708</v>
       </c>
@@ -12228,7 +12246,7 @@
       <c r="M194" s="4"/>
       <c r="N194" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="21">
+    <row r="195" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
         <v>711</v>
       </c>
@@ -12258,7 +12276,7 @@
         <v>632</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="21">
+    <row r="196" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
         <v>714</v>
       </c>
@@ -12288,7 +12306,7 @@
         <v>632</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="21">
+    <row r="197" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
         <v>715</v>
       </c>
@@ -12318,7 +12336,7 @@
         <v>632</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="21">
+    <row r="198" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
         <v>716</v>
       </c>
@@ -12348,7 +12366,7 @@
         <v>632</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="21">
+    <row r="199" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
         <v>718</v>
       </c>
@@ -12380,7 +12398,7 @@
         <v>641</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="21">
+    <row r="200" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -12396,7 +12414,7 @@
       <c r="M200" s="4"/>
       <c r="N200" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="21">
+    <row r="201" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
         <v>722</v>
       </c>
@@ -12436,7 +12454,7 @@
       </c>
       <c r="N201" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="18.75">
+    <row r="202" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
         <v>725</v>
       </c>
@@ -12476,7 +12494,7 @@
       </c>
       <c r="N202" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="18.75">
+    <row r="203" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
         <v>729</v>
       </c>
@@ -12514,7 +12532,7 @@
       </c>
       <c r="N203" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="18.75">
+    <row r="204" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
         <v>732</v>
       </c>
@@ -12552,7 +12570,7 @@
       </c>
       <c r="N204" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="18.75">
+    <row r="205" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
         <v>735</v>
       </c>
@@ -12592,7 +12610,7 @@
       </c>
       <c r="N205" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="18.75">
+    <row r="206" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
         <v>739</v>
       </c>
@@ -12632,7 +12650,7 @@
       </c>
       <c r="N206" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="18.75">
+    <row r="207" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
         <v>743</v>
       </c>
@@ -12670,7 +12688,7 @@
       </c>
       <c r="N207" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="18.75">
+    <row r="208" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
         <v>745</v>
       </c>
@@ -12708,7 +12726,7 @@
       </c>
       <c r="N208" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="18.75">
+    <row r="209" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
         <v>748</v>
       </c>
@@ -12746,7 +12764,7 @@
       </c>
       <c r="N209" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="18.75">
+    <row r="210" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
         <v>752</v>
       </c>
@@ -12788,7 +12806,7 @@
       </c>
       <c r="N210" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="18.75">
+    <row r="211" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
         <v>756</v>
       </c>
@@ -12824,7 +12842,7 @@
       </c>
       <c r="N211" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="18.75">
+    <row r="212" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
         <v>758</v>
       </c>
@@ -12864,7 +12882,7 @@
       </c>
       <c r="N212" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="18.75">
+    <row r="213" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -12880,7 +12898,7 @@
       <c r="M213" s="4"/>
       <c r="N213" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="18.75">
+    <row r="214" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
         <v>762</v>
       </c>
@@ -12920,7 +12938,7 @@
       </c>
       <c r="N214" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="18.75">
+    <row r="215" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
         <v>768</v>
       </c>
@@ -12960,7 +12978,7 @@
       </c>
       <c r="N215" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="18.75">
+    <row r="216" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
         <v>771</v>
       </c>
@@ -13000,7 +13018,7 @@
       </c>
       <c r="N216" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="18.75">
+    <row r="217" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
         <v>775</v>
       </c>
@@ -13040,7 +13058,7 @@
       </c>
       <c r="N217" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="18.75">
+    <row r="218" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
         <v>779</v>
       </c>
@@ -13080,7 +13098,7 @@
       </c>
       <c r="N218" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="18.75">
+    <row r="219" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="s">
         <v>782</v>
       </c>
@@ -13120,7 +13138,7 @@
       </c>
       <c r="N219" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="18.75">
+    <row r="220" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="s">
         <v>784</v>
       </c>
@@ -13160,7 +13178,7 @@
       </c>
       <c r="N220" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="18.75">
+    <row r="221" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="4" t="s">
         <v>786</v>
       </c>
@@ -13200,7 +13218,7 @@
       </c>
       <c r="N221" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="18.75">
+    <row r="222" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="4" t="s">
         <v>788</v>
       </c>
@@ -13238,7 +13256,7 @@
       </c>
       <c r="N222" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="18.75">
+    <row r="223" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="4" t="s">
         <v>792</v>
       </c>
@@ -13278,7 +13296,7 @@
       </c>
       <c r="N223" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="18.75">
+    <row r="224" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="4" t="s">
         <v>796</v>
       </c>
@@ -13320,7 +13338,7 @@
       </c>
       <c r="N224" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="18.75">
+    <row r="225" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
         <v>800</v>
       </c>
@@ -13360,7 +13378,7 @@
       </c>
       <c r="N225" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="18.75">
+    <row r="226" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
         <v>805</v>
       </c>
@@ -13400,7 +13418,7 @@
       </c>
       <c r="N226" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="18.75">
+    <row r="227" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
         <v>809</v>
       </c>
@@ -13442,7 +13460,7 @@
       </c>
       <c r="N227" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="18.75">
+    <row r="228" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="s">
         <v>811</v>
       </c>
@@ -13482,7 +13500,7 @@
       </c>
       <c r="N228" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="18.75">
+    <row r="229" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
         <v>815</v>
       </c>
@@ -13522,7 +13540,7 @@
       </c>
       <c r="N229" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="18.75">
+    <row r="230" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="s">
         <v>819</v>
       </c>
@@ -13562,7 +13580,7 @@
       </c>
       <c r="N230" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="18.75">
+    <row r="231" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
         <v>822</v>
       </c>
@@ -13598,7 +13616,7 @@
       </c>
       <c r="N231" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="18.75">
+    <row r="232" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
         <v>824</v>
       </c>
@@ -13636,7 +13654,7 @@
       </c>
       <c r="N232" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="18.75">
+    <row r="233" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
         <v>826</v>
       </c>
@@ -13674,7 +13692,7 @@
       </c>
       <c r="N233" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="18.75">
+    <row r="234" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
         <v>829</v>
       </c>
@@ -13708,7 +13726,7 @@
       </c>
       <c r="N234" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="18.75">
+    <row r="235" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
         <v>831</v>
       </c>
@@ -13748,7 +13766,7 @@
       </c>
       <c r="N235" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="18.75">
+    <row r="236" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="s">
         <v>835</v>
       </c>
@@ -13790,7 +13808,7 @@
         <v>840</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="18.75">
+    <row r="237" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
         <v>841</v>
       </c>
@@ -13828,7 +13846,7 @@
         <v>840</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="18.75">
+    <row r="238" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="s">
         <v>844</v>
       </c>
@@ -13870,7 +13888,7 @@
         <v>840</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="18.75">
+    <row r="239" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
         <v>849</v>
       </c>
@@ -13914,7 +13932,7 @@
         <v>854</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="18.75">
+    <row r="240" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -13930,7 +13948,7 @@
       <c r="M240" s="4"/>
       <c r="N240" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="18.75">
+    <row r="241" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
         <v>855</v>
       </c>
@@ -13960,7 +13978,7 @@
       <c r="M241" s="4"/>
       <c r="N241" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="18.75">
+    <row r="242" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
         <v>859</v>
       </c>
@@ -13990,7 +14008,7 @@
       <c r="M242" s="4"/>
       <c r="N242" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="18.75">
+    <row r="243" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
         <v>861</v>
       </c>
@@ -14020,7 +14038,7 @@
       <c r="M243" s="4"/>
       <c r="N243" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="18.75">
+    <row r="244" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="4" t="s">
         <v>863</v>
       </c>
@@ -14050,7 +14068,7 @@
       <c r="M244" s="4"/>
       <c r="N244" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="18.75">
+    <row r="245" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
         <v>865</v>
       </c>
@@ -14078,7 +14096,7 @@
       <c r="M245" s="4"/>
       <c r="N245" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="18.75">
+    <row r="246" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
         <v>867</v>
       </c>
@@ -14108,7 +14126,7 @@
       <c r="M246" s="4"/>
       <c r="N246" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="18.75">
+    <row r="247" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
         <v>870</v>
       </c>
@@ -14138,7 +14156,7 @@
       <c r="M247" s="4"/>
       <c r="N247" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="18.75">
+    <row r="248" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="4" t="s">
         <v>873</v>
       </c>
@@ -14168,7 +14186,7 @@
       <c r="M248" s="4"/>
       <c r="N248" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="18.75">
+    <row r="249" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
         <v>876</v>
       </c>
@@ -14198,7 +14216,7 @@
       <c r="M249" s="4"/>
       <c r="N249" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="18.75">
+    <row r="250" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="4" t="s">
         <v>878</v>
       </c>
@@ -14228,7 +14246,7 @@
       <c r="M250" s="4"/>
       <c r="N250" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="18.75">
+    <row r="251" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
         <v>880</v>
       </c>
@@ -14258,7 +14276,7 @@
       <c r="M251" s="4"/>
       <c r="N251" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="18.75">
+    <row r="252" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
         <v>882</v>
       </c>
@@ -14288,7 +14306,7 @@
       <c r="M252" s="4"/>
       <c r="N252" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="18.75">
+    <row r="253" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
         <v>883</v>
       </c>
@@ -14316,7 +14334,7 @@
       <c r="M253" s="4"/>
       <c r="N253" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="18.75">
+    <row r="254" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="4" t="s">
         <v>885</v>
       </c>
@@ -14344,7 +14362,7 @@
       <c r="M254" s="4"/>
       <c r="N254" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="18.75">
+    <row r="255" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
         <v>888</v>
       </c>
@@ -14374,7 +14392,7 @@
       <c r="M255" s="4"/>
       <c r="N255" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="18.75">
+    <row r="256" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
         <v>892</v>
       </c>
@@ -14402,7 +14420,7 @@
       <c r="M256" s="4"/>
       <c r="N256" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="18.75">
+    <row r="257" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
         <v>894</v>
       </c>
@@ -14432,7 +14450,7 @@
       <c r="M257" s="4"/>
       <c r="N257" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="18.75">
+    <row r="258" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
         <v>898</v>
       </c>
@@ -14462,7 +14480,7 @@
       <c r="M258" s="4"/>
       <c r="N258" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="18.75">
+    <row r="259" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
         <v>901</v>
       </c>
@@ -14492,7 +14510,7 @@
       <c r="M259" s="4"/>
       <c r="N259" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="18.75">
+    <row r="260" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
         <v>905</v>
       </c>
@@ -14520,7 +14538,7 @@
       <c r="M260" s="4"/>
       <c r="N260" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="18.75">
+    <row r="261" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
         <v>908</v>
       </c>
@@ -14550,7 +14568,7 @@
       <c r="M261" s="4"/>
       <c r="N261" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="18.75">
+    <row r="262" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="4" t="s">
         <v>912</v>
       </c>
@@ -14580,7 +14598,7 @@
       <c r="M262" s="4"/>
       <c r="N262" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="18.75">
+    <row r="263" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
         <v>915</v>
       </c>
@@ -14612,7 +14630,7 @@
         <v>854</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="18.75">
+    <row r="264" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
         <v>919</v>
       </c>
@@ -14644,7 +14662,7 @@
         <v>854</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="18.75">
+    <row r="265" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="4"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
@@ -14660,7 +14678,7 @@
       <c r="M265" s="4"/>
       <c r="N265" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="18.75">
+    <row r="266" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
         <v>923</v>
       </c>
@@ -14698,7 +14716,7 @@
       </c>
       <c r="N266" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="18.75">
+    <row r="267" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
         <v>927</v>
       </c>
@@ -14736,7 +14754,7 @@
       </c>
       <c r="N267" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="18.75">
+    <row r="268" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="4" t="s">
         <v>930</v>
       </c>
@@ -14776,7 +14794,7 @@
       </c>
       <c r="N268" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="18.75">
+    <row r="269" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="4" t="s">
         <v>934</v>
       </c>
@@ -14816,7 +14834,7 @@
       </c>
       <c r="N269" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="18.75">
+    <row r="270" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="4" t="s">
         <v>938</v>
       </c>
@@ -14856,7 +14874,7 @@
       </c>
       <c r="N270" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="18.75">
+    <row r="271" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
         <v>942</v>
       </c>
@@ -14896,7 +14914,7 @@
       </c>
       <c r="N271" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="18.75">
+    <row r="272" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="4" t="s">
         <v>944</v>
       </c>
@@ -14934,7 +14952,7 @@
       </c>
       <c r="N272" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="18.75">
+    <row r="273" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
         <v>947</v>
       </c>
@@ -14974,7 +14992,7 @@
       </c>
       <c r="N273" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="18.75">
+    <row r="274" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
         <v>951</v>
       </c>
@@ -15014,7 +15032,7 @@
       </c>
       <c r="N274" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="18.75">
+    <row r="275" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="4" t="s">
         <v>955</v>
       </c>
@@ -15054,7 +15072,7 @@
       </c>
       <c r="N275" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="18.75">
+    <row r="276" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="4" t="s">
         <v>959</v>
       </c>
@@ -15092,7 +15110,7 @@
       </c>
       <c r="N276" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="18.75">
+    <row r="277" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
         <v>962</v>
       </c>
@@ -15132,7 +15150,7 @@
         <v>840</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="18.75">
+    <row r="278" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
         <v>965</v>
       </c>
@@ -15174,7 +15192,7 @@
         <v>854</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="18.75">
+    <row r="279" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
@@ -15190,7 +15208,7 @@
       <c r="M279" s="4"/>
       <c r="N279" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="18.75">
+    <row r="280" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
         <v>970</v>
       </c>
@@ -15228,7 +15246,7 @@
       </c>
       <c r="N280" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="18.75">
+    <row r="281" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
         <v>236</v>
       </c>
@@ -15268,7 +15286,7 @@
       </c>
       <c r="N281" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="18.75">
+    <row r="282" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
         <v>976</v>
       </c>
@@ -15308,7 +15326,7 @@
       </c>
       <c r="N282" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="18.75">
+    <row r="283" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
         <v>980</v>
       </c>
@@ -15348,7 +15366,7 @@
       </c>
       <c r="N283" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="284" customHeight="1" ht="18.75">
+    <row r="284" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
         <v>983</v>
       </c>
@@ -15388,7 +15406,7 @@
       </c>
       <c r="N284" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="285" customHeight="1" ht="18.75">
+    <row r="285" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
         <v>987</v>
       </c>
@@ -15426,7 +15444,7 @@
       </c>
       <c r="N285" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="286" customHeight="1" ht="18.75">
+    <row r="286" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="4" t="s">
         <v>991</v>
       </c>
@@ -15464,7 +15482,7 @@
       </c>
       <c r="N286" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="287" customHeight="1" ht="18.75">
+    <row r="287" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
         <v>993</v>
       </c>
@@ -15502,7 +15520,7 @@
       </c>
       <c r="N287" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="288" customHeight="1" ht="18.75">
+    <row r="288" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
         <v>995</v>
       </c>
@@ -15540,7 +15558,7 @@
       </c>
       <c r="N288" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="18.75">
+    <row r="289" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
         <v>998</v>
       </c>
@@ -15580,7 +15598,7 @@
       </c>
       <c r="N289" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="290" customHeight="1" ht="18.75">
+    <row r="290" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="4" t="s">
         <v>1001</v>
       </c>
@@ -15618,7 +15636,7 @@
       </c>
       <c r="N290" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="18.75">
+    <row r="291" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
         <v>1003</v>
       </c>
@@ -15656,7 +15674,7 @@
       </c>
       <c r="N291" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="292" customHeight="1" ht="18.75">
+    <row r="292" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="4" t="s">
         <v>1005</v>
       </c>
@@ -15696,7 +15714,7 @@
       </c>
       <c r="N292" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="293" customHeight="1" ht="18.75">
+    <row r="293" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="4" t="s">
         <v>1009</v>
       </c>
@@ -15738,7 +15756,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="18.75">
+    <row r="294" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
@@ -15754,7 +15772,7 @@
       <c r="M294" s="4"/>
       <c r="N294" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="18.75">
+    <row r="295" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
         <v>1014</v>
       </c>
@@ -15784,7 +15802,7 @@
       <c r="M295" s="4"/>
       <c r="N295" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="296" customHeight="1" ht="18.75">
+    <row r="296" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="4" t="s">
         <v>1017</v>
       </c>
@@ -15814,7 +15832,7 @@
       <c r="M296" s="4"/>
       <c r="N296" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="18.75">
+    <row r="297" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="4" t="s">
         <v>1020</v>
       </c>
@@ -15844,7 +15862,7 @@
       <c r="M297" s="4"/>
       <c r="N297" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="298" customHeight="1" ht="18.75">
+    <row r="298" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="4" t="s">
         <v>1023</v>
       </c>
@@ -15874,7 +15892,7 @@
       <c r="M298" s="4"/>
       <c r="N298" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="299" customHeight="1" ht="18.75">
+    <row r="299" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="4" t="s">
         <v>1026</v>
       </c>
@@ -15904,7 +15922,7 @@
       <c r="M299" s="4"/>
       <c r="N299" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="18.75">
+    <row r="300" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="4" t="s">
         <v>1029</v>
       </c>
@@ -15934,7 +15952,7 @@
       <c r="M300" s="4"/>
       <c r="N300" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="18.75">
+    <row r="301" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="4" t="s">
         <v>1031</v>
       </c>
@@ -15964,7 +15982,7 @@
       <c r="M301" s="4"/>
       <c r="N301" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="302" customHeight="1" ht="18.75">
+    <row r="302" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="4" t="s">
         <v>1034</v>
       </c>
@@ -15994,7 +16012,7 @@
       <c r="M302" s="4"/>
       <c r="N302" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="303" customHeight="1" ht="18.75">
+    <row r="303" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="4" t="s">
         <v>1037</v>
       </c>
@@ -16024,7 +16042,7 @@
       <c r="M303" s="4"/>
       <c r="N303" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="304" customHeight="1" ht="18.75">
+    <row r="304" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="4" t="s">
         <v>1040</v>
       </c>
@@ -16054,7 +16072,7 @@
       <c r="M304" s="4"/>
       <c r="N304" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="18.75">
+    <row r="305" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="4" t="s">
         <v>1042</v>
       </c>
@@ -16084,7 +16102,7 @@
       <c r="M305" s="4"/>
       <c r="N305" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="306" customHeight="1" ht="18.75">
+    <row r="306" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="4" t="s">
         <v>1046</v>
       </c>
@@ -16114,7 +16132,7 @@
       <c r="M306" s="4"/>
       <c r="N306" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="307" customHeight="1" ht="18.75">
+    <row r="307" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="4" t="s">
         <v>1048</v>
       </c>
@@ -16144,7 +16162,7 @@
       <c r="M307" s="4"/>
       <c r="N307" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="18.75">
+    <row r="308" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="4" t="s">
         <v>1050</v>
       </c>
@@ -16174,7 +16192,7 @@
       <c r="M308" s="4"/>
       <c r="N308" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="309" customHeight="1" ht="18.75">
+    <row r="309" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="4" t="s">
         <v>1052</v>
       </c>
@@ -16204,7 +16222,7 @@
       <c r="M309" s="4"/>
       <c r="N309" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="18.75">
+    <row r="310" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="4" t="s">
         <v>1056</v>
       </c>
@@ -16234,7 +16252,7 @@
       <c r="M310" s="4"/>
       <c r="N310" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="18.75">
+    <row r="311" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="4" t="s">
         <v>1060</v>
       </c>
@@ -16264,7 +16282,7 @@
       <c r="M311" s="4"/>
       <c r="N311" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="18.75">
+    <row r="312" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="4" t="s">
         <v>1064</v>
       </c>
@@ -16294,7 +16312,7 @@
       <c r="M312" s="4"/>
       <c r="N312" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="18.75">
+    <row r="313" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="4" t="s">
         <v>1068</v>
       </c>
@@ -16326,7 +16344,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="18.75">
+    <row r="314" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="4" t="s">
         <v>1070</v>
       </c>
@@ -16358,7 +16376,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="18.75">
+    <row r="315" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="4" t="s">
         <v>1073</v>
       </c>
@@ -16390,7 +16408,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="316" customHeight="1" ht="18.75">
+    <row r="316" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="4" t="s">
         <v>1077</v>
       </c>
@@ -16422,7 +16440,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="317" customHeight="1" ht="18.75">
+    <row r="317" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="4" t="s">
         <v>1079</v>
       </c>
@@ -16454,7 +16472,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="18.75">
+    <row r="318" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
@@ -16470,7 +16488,7 @@
       <c r="M318" s="4"/>
       <c r="N318" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="319" customHeight="1" ht="18.75">
+    <row r="319" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="4" t="s">
         <v>1081</v>
       </c>
@@ -16510,7 +16528,7 @@
       </c>
       <c r="N319" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="320" customHeight="1" ht="18.75">
+    <row r="320" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="4" t="s">
         <v>1086</v>
       </c>
@@ -16548,7 +16566,7 @@
       </c>
       <c r="N320" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="18.75">
+    <row r="321" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="4" t="s">
         <v>1089</v>
       </c>
@@ -16586,7 +16604,7 @@
       </c>
       <c r="N321" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="18.75">
+    <row r="322" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="4" t="s">
         <v>1092</v>
       </c>
@@ -16626,7 +16644,7 @@
       </c>
       <c r="N322" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="323" customHeight="1" ht="18.75">
+    <row r="323" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="4" t="s">
         <v>1096</v>
       </c>
@@ -16664,7 +16682,7 @@
       </c>
       <c r="N323" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="18.75">
+    <row r="324" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="4" t="s">
         <v>1098</v>
       </c>
@@ -16702,7 +16720,7 @@
       </c>
       <c r="N324" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="325" customHeight="1" ht="18.75">
+    <row r="325" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="4" t="s">
         <v>1099</v>
       </c>
@@ -16740,7 +16758,7 @@
       </c>
       <c r="N325" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="326" customHeight="1" ht="18.75">
+    <row r="326" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="4" t="s">
         <v>1100</v>
       </c>
@@ -16782,7 +16800,7 @@
       </c>
       <c r="N326" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="18.75">
+    <row r="327" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="4" t="s">
         <v>1104</v>
       </c>
@@ -16826,7 +16844,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="328" customHeight="1" ht="18.75">
+    <row r="328" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="4" t="s">
         <v>1107</v>
       </c>
@@ -16868,7 +16886,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="329" customHeight="1" ht="18.75">
+    <row r="329" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="4" t="s">
         <v>1110</v>
       </c>
@@ -16910,7 +16928,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="330" customHeight="1" ht="18.75">
+    <row r="330" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
@@ -16926,7 +16944,7 @@
       <c r="M330" s="4"/>
       <c r="N330" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="331" customHeight="1" ht="18.75">
+    <row r="331" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="4" t="s">
         <v>1112</v>
       </c>
@@ -16964,7 +16982,7 @@
       </c>
       <c r="N331" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="332" customHeight="1" ht="18.75">
+    <row r="332" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="4" t="s">
         <v>1116</v>
       </c>
@@ -17004,7 +17022,7 @@
       </c>
       <c r="N332" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="333" customHeight="1" ht="18.75">
+    <row r="333" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="4" t="s">
         <v>1120</v>
       </c>
@@ -17044,7 +17062,7 @@
       </c>
       <c r="N333" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="18.75">
+    <row r="334" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="4" t="s">
         <v>1125</v>
       </c>
@@ -17082,7 +17100,7 @@
       </c>
       <c r="N334" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="18.75">
+    <row r="335" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="4" t="s">
         <v>1129</v>
       </c>
@@ -17122,7 +17140,7 @@
       </c>
       <c r="N335" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="336" customHeight="1" ht="18.75">
+    <row r="336" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="4" t="s">
         <v>1134</v>
       </c>
@@ -17162,7 +17180,7 @@
       </c>
       <c r="N336" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="337" customHeight="1" ht="18.75">
+    <row r="337" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="4" t="s">
         <v>1138</v>
       </c>
@@ -17204,7 +17222,7 @@
       </c>
       <c r="N337" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="338" customHeight="1" ht="18.75">
+    <row r="338" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="4" t="s">
         <v>1142</v>
       </c>
@@ -17244,7 +17262,7 @@
       </c>
       <c r="N338" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="339" customHeight="1" ht="18.75">
+    <row r="339" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="4" t="s">
         <v>1145</v>
       </c>
@@ -17286,7 +17304,7 @@
       </c>
       <c r="N339" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="340" customHeight="1" ht="18.75">
+    <row r="340" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="4" t="s">
         <v>1149</v>
       </c>
@@ -17328,7 +17346,7 @@
       </c>
       <c r="N340" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="341" customHeight="1" ht="18.75">
+    <row r="341" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="4" t="s">
         <v>1152</v>
       </c>
@@ -17368,7 +17386,7 @@
       </c>
       <c r="N341" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="342" customHeight="1" ht="18.75">
+    <row r="342" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -17384,7 +17402,7 @@
       <c r="M342" s="4"/>
       <c r="N342" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="343" customHeight="1" ht="18.75">
+    <row r="343" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="4" t="s">
         <v>1155</v>
       </c>
@@ -17414,7 +17432,7 @@
       <c r="M343" s="4"/>
       <c r="N343" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="344" customHeight="1" ht="18.75">
+    <row r="344" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="4" t="s">
         <v>1158</v>
       </c>
@@ -17444,7 +17462,7 @@
       <c r="M344" s="4"/>
       <c r="N344" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="345" customHeight="1" ht="18.75">
+    <row r="345" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="4" t="s">
         <v>1161</v>
       </c>
@@ -17474,7 +17492,7 @@
       <c r="M345" s="4"/>
       <c r="N345" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="346" customHeight="1" ht="18.75">
+    <row r="346" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="4" t="s">
         <v>1164</v>
       </c>
@@ -17504,7 +17522,7 @@
       <c r="M346" s="4"/>
       <c r="N346" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="347" customHeight="1" ht="18.75">
+    <row r="347" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="4" t="s">
         <v>1168</v>
       </c>
@@ -17534,7 +17552,7 @@
       <c r="M347" s="4"/>
       <c r="N347" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="348" customHeight="1" ht="18.75">
+    <row r="348" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="4" t="s">
         <v>1170</v>
       </c>
@@ -17564,7 +17582,7 @@
       <c r="M348" s="4"/>
       <c r="N348" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="349" customHeight="1" ht="18.75">
+    <row r="349" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="4" t="s">
         <v>1173</v>
       </c>
@@ -17594,7 +17612,7 @@
       <c r="M349" s="4"/>
       <c r="N349" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="350" customHeight="1" ht="18.75">
+    <row r="350" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="4" t="s">
         <v>1175</v>
       </c>
@@ -17624,7 +17642,7 @@
       <c r="M350" s="4"/>
       <c r="N350" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="351" customHeight="1" ht="18.75">
+    <row r="351" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="4" t="s">
         <v>1179</v>
       </c>
@@ -17654,7 +17672,7 @@
       <c r="M351" s="4"/>
       <c r="N351" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="352" customHeight="1" ht="18.75">
+    <row r="352" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="4" t="s">
         <v>1182</v>
       </c>
@@ -17684,7 +17702,7 @@
       <c r="M352" s="4"/>
       <c r="N352" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="353" customHeight="1" ht="18.75">
+    <row r="353" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="4" t="s">
         <v>1185</v>
       </c>
@@ -17714,7 +17732,7 @@
       <c r="M353" s="4"/>
       <c r="N353" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="354" customHeight="1" ht="18.75">
+    <row r="354" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="4" t="s">
         <v>1187</v>
       </c>
@@ -17744,7 +17762,7 @@
       <c r="M354" s="4"/>
       <c r="N354" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="355" customHeight="1" ht="18.75">
+    <row r="355" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="4" t="s">
         <v>1191</v>
       </c>
@@ -17774,7 +17792,7 @@
       <c r="M355" s="4"/>
       <c r="N355" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="356" customHeight="1" ht="18.75">
+    <row r="356" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="4"/>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
@@ -17790,7 +17808,7 @@
       <c r="M356" s="4"/>
       <c r="N356" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="357" customHeight="1" ht="18.75">
+    <row r="357" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="4" t="s">
         <v>1195</v>
       </c>
@@ -17830,7 +17848,7 @@
       </c>
       <c r="N357" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="358" customHeight="1" ht="18.75">
+    <row r="358" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="4" t="s">
         <v>1199</v>
       </c>
@@ -17870,7 +17888,7 @@
       </c>
       <c r="N358" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="359" customHeight="1" ht="18.75">
+    <row r="359" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="4" t="s">
         <v>1203</v>
       </c>
@@ -17908,7 +17926,7 @@
       </c>
       <c r="N359" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="360" customHeight="1" ht="18.75">
+    <row r="360" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="4" t="s">
         <v>1206</v>
       </c>
@@ -17948,7 +17966,7 @@
       </c>
       <c r="N360" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="361" customHeight="1" ht="18.75">
+    <row r="361" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="4" t="s">
         <v>1208</v>
       </c>
@@ -17988,7 +18006,7 @@
       </c>
       <c r="N361" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="362" customHeight="1" ht="18.75">
+    <row r="362" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="4" t="s">
         <v>1211</v>
       </c>
@@ -18028,7 +18046,7 @@
       </c>
       <c r="N362" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="363" customHeight="1" ht="18.75">
+    <row r="363" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="4" t="s">
         <v>1216</v>
       </c>
@@ -18068,7 +18086,7 @@
       </c>
       <c r="N363" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="364" customHeight="1" ht="18.75">
+    <row r="364" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="4" t="s">
         <v>1219</v>
       </c>
@@ -18108,7 +18126,7 @@
       </c>
       <c r="N364" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="365" customHeight="1" ht="18.75">
+    <row r="365" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="4" t="s">
         <v>1224</v>
       </c>
@@ -18150,7 +18168,7 @@
       </c>
       <c r="N365" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="366" customHeight="1" ht="18.75">
+    <row r="366" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="4"/>
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
@@ -18166,7 +18184,7 @@
       <c r="M366" s="4"/>
       <c r="N366" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="367" customHeight="1" ht="18.75">
+    <row r="367" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="4" t="s">
         <v>1227</v>
       </c>
@@ -18208,7 +18226,7 @@
       </c>
       <c r="N367" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="368" customHeight="1" ht="18.75">
+    <row r="368" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="4" t="s">
         <v>1232</v>
       </c>
@@ -18250,7 +18268,7 @@
       </c>
       <c r="N368" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="369" customHeight="1" ht="18.75">
+    <row r="369" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="4" t="s">
         <v>1235</v>
       </c>
@@ -18292,7 +18310,7 @@
       </c>
       <c r="N369" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="370" customHeight="1" ht="18.75">
+    <row r="370" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="4" t="s">
         <v>1240</v>
       </c>
@@ -18332,7 +18350,7 @@
       </c>
       <c r="N370" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="371" customHeight="1" ht="18.75">
+    <row r="371" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="4" t="s">
         <v>1244</v>
       </c>
@@ -18374,7 +18392,7 @@
       </c>
       <c r="N371" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="372" customHeight="1" ht="18.75">
+    <row r="372" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="4" t="s">
         <v>1249</v>
       </c>
@@ -18416,7 +18434,7 @@
       </c>
       <c r="N372" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="373" customHeight="1" ht="18.75">
+    <row r="373" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="4" t="s">
         <v>1253</v>
       </c>
@@ -18458,7 +18476,7 @@
       </c>
       <c r="N373" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="374" customHeight="1" ht="18.75">
+    <row r="374" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="4" t="s">
         <v>1257</v>
       </c>
@@ -18496,7 +18514,7 @@
       </c>
       <c r="N374" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="375" customHeight="1" ht="18.75">
+    <row r="375" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="4" t="s">
         <v>1262</v>
       </c>
@@ -18534,7 +18552,7 @@
       </c>
       <c r="N375" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="376" customHeight="1" ht="18.75">
+    <row r="376" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="4" t="s">
         <v>1266</v>
       </c>
@@ -18576,7 +18594,7 @@
       </c>
       <c r="N376" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="377" customHeight="1" ht="18.75">
+    <row r="377" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="4" t="s">
         <v>1269</v>
       </c>
@@ -18618,7 +18636,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="378" customHeight="1" ht="18.75">
+    <row r="378" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="4" t="s">
         <v>1272</v>
       </c>
@@ -18662,7 +18680,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="379" customHeight="1" ht="18.75">
+    <row r="379" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="4" t="s">
         <v>1277</v>
       </c>
@@ -18706,7 +18724,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="380" customHeight="1" ht="18.75">
+    <row r="380" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="4" t="s">
         <v>1280</v>
       </c>
@@ -18750,7 +18768,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="381" customHeight="1" ht="18.75">
+    <row r="381" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="4"/>
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
@@ -18766,7 +18784,7 @@
       <c r="M381" s="4"/>
       <c r="N381" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="382" customHeight="1" ht="18.75">
+    <row r="382" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="4" t="s">
         <v>1284</v>
       </c>
@@ -18796,7 +18814,7 @@
       <c r="M382" s="4"/>
       <c r="N382" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="383" customHeight="1" ht="18.75">
+    <row r="383" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="4" t="s">
         <v>1288</v>
       </c>
@@ -18826,7 +18844,7 @@
       <c r="M383" s="4"/>
       <c r="N383" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="384" customHeight="1" ht="18.75">
+    <row r="384" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="4" t="s">
         <v>1290</v>
       </c>
@@ -18856,7 +18874,7 @@
       <c r="M384" s="4"/>
       <c r="N384" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="385" customHeight="1" ht="18.75">
+    <row r="385" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="4" t="s">
         <v>1293</v>
       </c>
@@ -18886,7 +18904,7 @@
       <c r="M385" s="4"/>
       <c r="N385" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="386" customHeight="1" ht="18.75">
+    <row r="386" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="4" t="s">
         <v>1297</v>
       </c>
@@ -18916,7 +18934,7 @@
       <c r="M386" s="4"/>
       <c r="N386" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="387" customHeight="1" ht="18.75">
+    <row r="387" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="4" t="s">
         <v>1301</v>
       </c>
@@ -18946,7 +18964,7 @@
       <c r="M387" s="4"/>
       <c r="N387" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="388" customHeight="1" ht="18.75">
+    <row r="388" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="4" t="s">
         <v>1305</v>
       </c>
@@ -18976,7 +18994,7 @@
       <c r="M388" s="4"/>
       <c r="N388" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="389" customHeight="1" ht="18.75">
+    <row r="389" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="4" t="s">
         <v>1307</v>
       </c>
@@ -19006,7 +19024,7 @@
       <c r="M389" s="4"/>
       <c r="N389" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="390" customHeight="1" ht="18.75">
+    <row r="390" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="4" t="s">
         <v>1311</v>
       </c>
@@ -19036,7 +19054,7 @@
       <c r="M390" s="4"/>
       <c r="N390" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="391" customHeight="1" ht="18.75">
+    <row r="391" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="4" t="s">
         <v>1314</v>
       </c>
@@ -19066,7 +19084,7 @@
       <c r="M391" s="4"/>
       <c r="N391" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="392" customHeight="1" ht="18.75">
+    <row r="392" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="4" t="s">
         <v>1317</v>
       </c>
@@ -19096,7 +19114,7 @@
       <c r="M392" s="4"/>
       <c r="N392" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="393" customHeight="1" ht="18.75">
+    <row r="393" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="4" t="s">
         <v>1320</v>
       </c>
@@ -19126,7 +19144,7 @@
       <c r="M393" s="4"/>
       <c r="N393" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="394" customHeight="1" ht="18.75">
+    <row r="394" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="4" t="s">
         <v>1323</v>
       </c>
@@ -19156,7 +19174,7 @@
       <c r="M394" s="4"/>
       <c r="N394" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="395" customHeight="1" ht="18.75">
+    <row r="395" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="4" t="s">
         <v>1327</v>
       </c>
@@ -19186,7 +19204,7 @@
       <c r="M395" s="4"/>
       <c r="N395" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="396" customHeight="1" ht="18.75">
+    <row r="396" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="4" t="s">
         <v>1330</v>
       </c>
@@ -19216,7 +19234,7 @@
       <c r="M396" s="4"/>
       <c r="N396" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="397" customHeight="1" ht="18.75">
+    <row r="397" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="4" t="s">
         <v>1334</v>
       </c>
@@ -19246,7 +19264,7 @@
       <c r="M397" s="4"/>
       <c r="N397" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="398" customHeight="1" ht="18.75">
+    <row r="398" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="4" t="s">
         <v>1338</v>
       </c>
@@ -19276,7 +19294,7 @@
       <c r="M398" s="4"/>
       <c r="N398" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="399" customHeight="1" ht="18.75">
+    <row r="399" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="4" t="s">
         <v>1342</v>
       </c>
@@ -19306,7 +19324,7 @@
       <c r="M399" s="4"/>
       <c r="N399" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="400" customHeight="1" ht="18.75">
+    <row r="400" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="4" t="s">
         <v>1345</v>
       </c>
@@ -19336,7 +19354,7 @@
       <c r="M400" s="4"/>
       <c r="N400" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="401" customHeight="1" ht="18.75">
+    <row r="401" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="4" t="s">
         <v>1348</v>
       </c>
@@ -19366,7 +19384,7 @@
       <c r="M401" s="4"/>
       <c r="N401" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="402" customHeight="1" ht="18.75">
+    <row r="402" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="4"/>
       <c r="B402" s="4"/>
       <c r="C402" s="4"/>
@@ -19382,7 +19400,7 @@
       <c r="M402" s="4"/>
       <c r="N402" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="403" customHeight="1" ht="18.75">
+    <row r="403" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="4" t="s">
         <v>1350</v>
       </c>
@@ -19424,7 +19442,7 @@
       </c>
       <c r="N403" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="404" customHeight="1" ht="18.75">
+    <row r="404" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="4" t="s">
         <v>1352</v>
       </c>
@@ -19464,7 +19482,7 @@
       </c>
       <c r="N404" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="405" customHeight="1" ht="18.75">
+    <row r="405" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="4" t="s">
         <v>1355</v>
       </c>
@@ -19504,7 +19522,7 @@
       </c>
       <c r="N405" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="406" customHeight="1" ht="18.75">
+    <row r="406" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="4" t="s">
         <v>1360</v>
       </c>
@@ -19544,7 +19562,7 @@
       </c>
       <c r="N406" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="407" customHeight="1" ht="18.75">
+    <row r="407" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="4" t="s">
         <v>1363</v>
       </c>
@@ -19584,7 +19602,7 @@
       </c>
       <c r="N407" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="408" customHeight="1" ht="18.75">
+    <row r="408" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="4" t="s">
         <v>1369</v>
       </c>
@@ -19624,7 +19642,7 @@
       </c>
       <c r="N408" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="409" customHeight="1" ht="18.75">
+    <row r="409" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="4" t="s">
         <v>1374</v>
       </c>
@@ -19664,7 +19682,7 @@
       </c>
       <c r="N409" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="410" customHeight="1" ht="18.75">
+    <row r="410" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="4" t="s">
         <v>1377</v>
       </c>
@@ -19706,7 +19724,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="411" customHeight="1" ht="18.75">
+    <row r="411" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="4" t="s">
         <v>1379</v>
       </c>
@@ -19748,7 +19766,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="412" customHeight="1" ht="18.75">
+    <row r="412" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="4" t="s">
         <v>1382</v>
       </c>
@@ -19790,7 +19808,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="413" customHeight="1" ht="18.75">
+    <row r="413" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="6"/>
       <c r="B413" s="6"/>
       <c r="C413" s="6"/>
@@ -19806,29 +19824,29 @@
       <c r="M413" s="6"/>
       <c r="N413" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="414" customHeight="1" ht="18.75">
-      <c r="A414" s="8" t="s">
+    <row r="414" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A414" s="12" t="s">
         <v>1384</v>
       </c>
-      <c r="B414" s="9"/>
+      <c r="B414" s="13"/>
       <c r="C414" s="6"/>
-      <c r="D414" s="10" t="s">
+      <c r="D414" s="14" t="s">
         <v>1385</v>
       </c>
-      <c r="E414" s="9"/>
-      <c r="F414" s="9"/>
-      <c r="G414" s="9"/>
-      <c r="H414" s="11"/>
-      <c r="I414" s="11"/>
-      <c r="J414" s="9"/>
-      <c r="K414" s="9"/>
-      <c r="L414" s="9"/>
-      <c r="M414" s="9"/>
+      <c r="E414" s="13"/>
+      <c r="F414" s="13"/>
+      <c r="G414" s="13"/>
+      <c r="H414" s="15"/>
+      <c r="I414" s="15"/>
+      <c r="J414" s="13"/>
+      <c r="K414" s="13"/>
+      <c r="L414" s="13"/>
+      <c r="M414" s="13"/>
       <c r="N414" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="415" customHeight="1" ht="18.75">
-      <c r="A415" s="9"/>
-      <c r="B415" s="9"/>
+    <row r="415" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A415" s="13"/>
+      <c r="B415" s="13"/>
       <c r="C415" s="6"/>
       <c r="D415" s="7"/>
       <c r="E415" s="6"/>
@@ -19842,3175 +19860,3159 @@
       <c r="M415" s="6"/>
       <c r="N415" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="416" customHeight="1" ht="18.75">
-      <c r="A416" s="12" t="s">
+    <row r="416" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A416" s="8" t="s">
         <v>1386</v>
       </c>
-      <c r="B416" s="12" t="s">
+      <c r="B416" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C416" s="12" t="s">
+      <c r="C416" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D416" s="13">
-        <v>22</v>
-      </c>
-      <c r="E416" s="12" t="s">
+      <c r="D416" s="9">
+        <v>22</v>
+      </c>
+      <c r="E416" s="8" t="s">
         <v>1388</v>
       </c>
-      <c r="F416" s="12" t="s">
+      <c r="F416" s="8" t="s">
         <v>1389</v>
       </c>
-      <c r="G416" s="12" t="s">
+      <c r="G416" s="8" t="s">
         <v>1390</v>
       </c>
-      <c r="H416" s="13">
+      <c r="H416" s="9">
         <v>6</v>
       </c>
-      <c r="I416" s="13"/>
-      <c r="J416" s="12" t="s">
+      <c r="I416" s="9"/>
+      <c r="J416" s="8" t="s">
         <v>937</v>
       </c>
-      <c r="K416" s="12" t="s">
+      <c r="K416" s="8" t="s">
         <v>1215</v>
       </c>
-      <c r="L416" s="12" t="s">
+      <c r="L416" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="M416" s="12" t="s">
+      <c r="M416" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="N416" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="417" customHeight="1" ht="18.75">
-      <c r="A417" s="12" t="s">
+      <c r="N416" s="8"/>
+    </row>
+    <row r="417" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A417" s="8" t="s">
         <v>1392</v>
       </c>
-      <c r="B417" s="12" t="s">
+      <c r="B417" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C417" s="12" t="s">
+      <c r="C417" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D417" s="13">
-        <v>22</v>
-      </c>
-      <c r="E417" s="12" t="s">
+      <c r="D417" s="9">
+        <v>22</v>
+      </c>
+      <c r="E417" s="8" t="s">
         <v>1393</v>
       </c>
-      <c r="F417" s="12" t="s">
+      <c r="F417" s="8" t="s">
         <v>1394</v>
       </c>
-      <c r="G417" s="12" t="s">
+      <c r="G417" s="8" t="s">
         <v>1012</v>
       </c>
-      <c r="H417" s="13">
+      <c r="H417" s="9">
         <v>5</v>
       </c>
-      <c r="I417" s="13"/>
-      <c r="J417" s="12" t="s">
+      <c r="I417" s="9"/>
+      <c r="J417" s="8" t="s">
         <v>791</v>
       </c>
-      <c r="K417" s="12" t="s">
+      <c r="K417" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L417" s="12" t="s">
+      <c r="L417" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="M417" s="12" t="s">
+      <c r="M417" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="N417" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="418" customHeight="1" ht="18.75">
-      <c r="A418" s="12" t="s">
+      <c r="N417" s="8"/>
+    </row>
+    <row r="418" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A418" s="8" t="s">
         <v>1395</v>
       </c>
-      <c r="B418" s="12" t="s">
+      <c r="B418" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C418" s="12" t="s">
+      <c r="C418" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D418" s="13">
-        <v>22</v>
-      </c>
-      <c r="E418" s="12" t="s">
+      <c r="D418" s="9">
+        <v>22</v>
+      </c>
+      <c r="E418" s="8" t="s">
         <v>1396</v>
       </c>
-      <c r="F418" s="12" t="s">
+      <c r="F418" s="8" t="s">
         <v>568</v>
       </c>
-      <c r="G418" s="12" t="s">
+      <c r="G418" s="8" t="s">
         <v>1397</v>
       </c>
-      <c r="H418" s="13">
+      <c r="H418" s="9">
         <v>4</v>
       </c>
-      <c r="I418" s="13"/>
-      <c r="J418" s="12" t="s">
+      <c r="I418" s="9"/>
+      <c r="J418" s="8" t="s">
         <v>937</v>
       </c>
-      <c r="K418" s="12" t="s">
+      <c r="K418" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L418" s="12" t="s">
+      <c r="L418" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="M418" s="12" t="s">
+      <c r="M418" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="N418" s="12" t="s">
+      <c r="N418" s="8" t="s">
         <v>1398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="419" customHeight="1" ht="18.75">
-      <c r="A419" s="12" t="s">
+    <row r="419" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A419" s="8" t="s">
         <v>1399</v>
       </c>
-      <c r="B419" s="12" t="s">
+      <c r="B419" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C419" s="12" t="s">
+      <c r="C419" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D419" s="13">
-        <v>22</v>
-      </c>
-      <c r="E419" s="12" t="s">
+      <c r="D419" s="9">
+        <v>22</v>
+      </c>
+      <c r="E419" s="8" t="s">
         <v>1400</v>
       </c>
-      <c r="F419" s="12" t="s">
+      <c r="F419" s="8" t="s">
         <v>1401</v>
       </c>
-      <c r="G419" s="12" t="s">
+      <c r="G419" s="8" t="s">
         <v>1402</v>
       </c>
-      <c r="H419" s="13">
+      <c r="H419" s="9">
         <v>5</v>
       </c>
-      <c r="I419" s="13"/>
-      <c r="J419" s="12" t="s">
+      <c r="I419" s="9"/>
+      <c r="J419" s="8" t="s">
         <v>937</v>
       </c>
-      <c r="K419" s="12" t="s">
+      <c r="K419" s="8" t="s">
         <v>1215</v>
       </c>
-      <c r="L419" s="12" t="s">
+      <c r="L419" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="M419" s="12" t="s">
+      <c r="M419" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="N419" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="420" customHeight="1" ht="18.75">
-      <c r="A420" s="12" t="s">
+      <c r="N419" s="8"/>
+    </row>
+    <row r="420" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A420" s="8" t="s">
         <v>1403</v>
       </c>
-      <c r="B420" s="12" t="s">
+      <c r="B420" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C420" s="12" t="s">
+      <c r="C420" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D420" s="13">
-        <v>22</v>
-      </c>
-      <c r="E420" s="12" t="s">
+      <c r="D420" s="9">
+        <v>22</v>
+      </c>
+      <c r="E420" s="8" t="s">
         <v>1404</v>
       </c>
-      <c r="F420" s="12" t="s">
+      <c r="F420" s="8" t="s">
         <v>1401</v>
       </c>
-      <c r="G420" s="12" t="s">
+      <c r="G420" s="8" t="s">
         <v>1405</v>
       </c>
-      <c r="H420" s="13">
+      <c r="H420" s="9">
         <v>3</v>
       </c>
-      <c r="I420" s="13"/>
-      <c r="J420" s="12" t="s">
+      <c r="I420" s="9"/>
+      <c r="J420" s="8" t="s">
         <v>791</v>
       </c>
-      <c r="K420" s="12" t="s">
+      <c r="K420" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L420" s="12" t="s">
+      <c r="L420" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="M420" s="12" t="s">
+      <c r="M420" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="N420" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="421" customHeight="1" ht="18.75">
-      <c r="A421" s="12" t="s">
+      <c r="N420" s="8"/>
+    </row>
+    <row r="421" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A421" s="8" t="s">
         <v>1406</v>
       </c>
-      <c r="B421" s="12" t="s">
+      <c r="B421" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C421" s="12" t="s">
+      <c r="C421" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D421" s="13">
-        <v>22</v>
-      </c>
-      <c r="E421" s="12" t="s">
+      <c r="D421" s="9">
+        <v>22</v>
+      </c>
+      <c r="E421" s="8" t="s">
         <v>1407</v>
       </c>
-      <c r="F421" s="12" t="s">
+      <c r="F421" s="8" t="s">
         <v>1408</v>
       </c>
-      <c r="G421" s="12" t="s">
+      <c r="G421" s="8" t="s">
         <v>1409</v>
       </c>
-      <c r="H421" s="13">
+      <c r="H421" s="9">
         <v>5</v>
       </c>
-      <c r="I421" s="13"/>
-      <c r="J421" s="12" t="s">
+      <c r="I421" s="9"/>
+      <c r="J421" s="8" t="s">
         <v>937</v>
       </c>
-      <c r="K421" s="12" t="s">
+      <c r="K421" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L421" s="12" t="s">
+      <c r="L421" s="8" t="s">
         <v>1410</v>
       </c>
-      <c r="M421" s="12" t="s">
+      <c r="M421" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="N421" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="422" customHeight="1" ht="18.75">
-      <c r="A422" s="12" t="s">
+      <c r="N421" s="8"/>
+    </row>
+    <row r="422" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A422" s="8" t="s">
         <v>1411</v>
       </c>
-      <c r="B422" s="12" t="s">
+      <c r="B422" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C422" s="12" t="s">
+      <c r="C422" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D422" s="13">
-        <v>22</v>
-      </c>
-      <c r="E422" s="12" t="s">
+      <c r="D422" s="9">
+        <v>22</v>
+      </c>
+      <c r="E422" s="8" t="s">
         <v>1412</v>
       </c>
-      <c r="F422" s="12" t="s">
+      <c r="F422" s="8" t="s">
         <v>1413</v>
       </c>
-      <c r="G422" s="12" t="s">
+      <c r="G422" s="8" t="s">
         <v>567</v>
       </c>
-      <c r="H422" s="13">
+      <c r="H422" s="9">
         <v>3</v>
       </c>
-      <c r="I422" s="13"/>
-      <c r="J422" s="12" t="s">
+      <c r="I422" s="9"/>
+      <c r="J422" s="8" t="s">
         <v>969</v>
       </c>
-      <c r="K422" s="12" t="s">
+      <c r="K422" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L422" s="12" t="s">
+      <c r="L422" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M422" s="12" t="s">
+      <c r="M422" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="N422" s="12" t="s">
+      <c r="N422" s="8" t="s">
         <v>1398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="423" customHeight="1" ht="18.75">
-      <c r="A423" s="12" t="s">
+    <row r="423" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A423" s="8" t="s">
         <v>1414</v>
       </c>
-      <c r="B423" s="12" t="s">
+      <c r="B423" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C423" s="12" t="s">
+      <c r="C423" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D423" s="13">
-        <v>22</v>
-      </c>
-      <c r="E423" s="12" t="s">
+      <c r="D423" s="9">
+        <v>22</v>
+      </c>
+      <c r="E423" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F423" s="12" t="s">
+      <c r="F423" s="8" t="s">
         <v>1415</v>
       </c>
-      <c r="G423" s="12" t="s">
+      <c r="G423" s="8" t="s">
         <v>1416</v>
       </c>
-      <c r="H423" s="13">
+      <c r="H423" s="9">
         <v>4</v>
       </c>
-      <c r="I423" s="13">
+      <c r="I423" s="9">
         <v>3</v>
       </c>
-      <c r="J423" s="12" t="s">
+      <c r="J423" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="K423" s="12" t="s">
+      <c r="K423" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L423" s="12" t="s">
+      <c r="L423" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="M423" s="12" t="s">
+      <c r="M423" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="N423" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="424" customHeight="1" ht="18.75">
-      <c r="A424" s="12" t="s">
+      <c r="N423" s="8"/>
+    </row>
+    <row r="424" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A424" s="8" t="s">
         <v>1417</v>
       </c>
-      <c r="B424" s="12" t="s">
+      <c r="B424" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C424" s="12" t="s">
+      <c r="C424" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D424" s="13">
-        <v>22</v>
-      </c>
-      <c r="E424" s="12" t="s">
+      <c r="D424" s="9">
+        <v>22</v>
+      </c>
+      <c r="E424" s="8" t="s">
         <v>1418</v>
       </c>
-      <c r="F424" s="12" t="s">
+      <c r="F424" s="8" t="s">
         <v>1207</v>
       </c>
-      <c r="G424" s="12" t="s">
+      <c r="G424" s="8" t="s">
         <v>1419</v>
       </c>
-      <c r="H424" s="13">
+      <c r="H424" s="9">
         <v>3</v>
       </c>
-      <c r="I424" s="13">
+      <c r="I424" s="9">
         <v>4</v>
       </c>
-      <c r="J424" s="12" t="s">
+      <c r="J424" s="8" t="s">
         <v>979</v>
       </c>
-      <c r="K424" s="12" t="s">
+      <c r="K424" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L424" s="12" t="s">
+      <c r="L424" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="M424" s="12" t="s">
+      <c r="M424" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="N424" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="425" customHeight="1" ht="18.75">
-      <c r="A425" s="12" t="s">
+      <c r="N424" s="8"/>
+    </row>
+    <row r="425" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A425" s="8" t="s">
         <v>1420</v>
       </c>
-      <c r="B425" s="12" t="s">
+      <c r="B425" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C425" s="12" t="s">
+      <c r="C425" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D425" s="13">
-        <v>22</v>
-      </c>
-      <c r="E425" s="12" t="s">
+      <c r="D425" s="9">
+        <v>22</v>
+      </c>
+      <c r="E425" s="8" t="s">
         <v>1421</v>
       </c>
-      <c r="F425" s="12" t="s">
+      <c r="F425" s="8" t="s">
         <v>1422</v>
       </c>
-      <c r="G425" s="12" t="s">
+      <c r="G425" s="8" t="s">
         <v>1423</v>
       </c>
-      <c r="H425" s="13">
+      <c r="H425" s="9">
         <v>3</v>
       </c>
-      <c r="I425" s="13">
+      <c r="I425" s="9">
         <v>4</v>
       </c>
-      <c r="J425" s="12" t="s">
+      <c r="J425" s="8" t="s">
         <v>973</v>
       </c>
-      <c r="K425" s="12" t="s">
+      <c r="K425" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L425" s="12" t="s">
+      <c r="L425" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="M425" s="12" t="s">
+      <c r="M425" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="N425" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="426" customHeight="1" ht="18.75">
-      <c r="A426" s="12" t="s">
+      <c r="N425" s="8"/>
+    </row>
+    <row r="426" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A426" s="8" t="s">
         <v>1424</v>
       </c>
-      <c r="B426" s="12" t="s">
+      <c r="B426" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C426" s="12" t="s">
+      <c r="C426" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D426" s="13">
-        <v>22</v>
-      </c>
-      <c r="E426" s="12" t="s">
+      <c r="D426" s="9">
+        <v>22</v>
+      </c>
+      <c r="E426" s="8" t="s">
         <v>1425</v>
       </c>
-      <c r="F426" s="12" t="s">
+      <c r="F426" s="8" t="s">
         <v>1426</v>
       </c>
-      <c r="G426" s="12" t="s">
+      <c r="G426" s="8" t="s">
         <v>1423</v>
       </c>
-      <c r="H426" s="13">
+      <c r="H426" s="9">
         <v>2</v>
       </c>
-      <c r="I426" s="13"/>
-      <c r="J426" s="12" t="s">
+      <c r="I426" s="9"/>
+      <c r="J426" s="8" t="s">
         <v>1427</v>
       </c>
-      <c r="K426" s="12" t="s">
+      <c r="K426" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L426" s="12" t="s">
+      <c r="L426" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="M426" s="12" t="s">
+      <c r="M426" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="N426" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="427" customHeight="1" ht="18.75">
-      <c r="A427" s="12" t="s">
+      <c r="N426" s="8"/>
+    </row>
+    <row r="427" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A427" s="8" t="s">
         <v>1428</v>
       </c>
-      <c r="B427" s="12" t="s">
+      <c r="B427" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C427" s="12" t="s">
+      <c r="C427" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D427" s="13">
-        <v>22</v>
-      </c>
-      <c r="E427" s="12" t="s">
+      <c r="D427" s="9">
+        <v>22</v>
+      </c>
+      <c r="E427" s="8" t="s">
         <v>1429</v>
       </c>
-      <c r="F427" s="12" t="s">
+      <c r="F427" s="8" t="s">
         <v>1430</v>
       </c>
-      <c r="G427" s="12" t="s">
+      <c r="G427" s="8" t="s">
         <v>1431</v>
       </c>
-      <c r="H427" s="13">
+      <c r="H427" s="9">
         <v>3</v>
       </c>
-      <c r="I427" s="13">
+      <c r="I427" s="9">
         <v>3</v>
       </c>
-      <c r="J427" s="12" t="s">
+      <c r="J427" s="8" t="s">
         <v>973</v>
       </c>
-      <c r="K427" s="12" t="s">
+      <c r="K427" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L427" s="12" t="s">
+      <c r="L427" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="M427" s="12" t="s">
+      <c r="M427" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="N427" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="428" customHeight="1" ht="18.75">
-      <c r="A428" s="12" t="s">
+      <c r="N427" s="8"/>
+    </row>
+    <row r="428" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A428" s="8" t="s">
         <v>1432</v>
       </c>
-      <c r="B428" s="12" t="s">
+      <c r="B428" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C428" s="12" t="s">
+      <c r="C428" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D428" s="13">
-        <v>22</v>
-      </c>
-      <c r="E428" s="12" t="s">
+      <c r="D428" s="9">
+        <v>22</v>
+      </c>
+      <c r="E428" s="8" t="s">
         <v>1433</v>
       </c>
-      <c r="F428" s="12" t="s">
+      <c r="F428" s="8" t="s">
         <v>1434</v>
       </c>
-      <c r="G428" s="12" t="s">
+      <c r="G428" s="8" t="s">
         <v>1012</v>
       </c>
-      <c r="H428" s="13">
+      <c r="H428" s="9">
         <v>3</v>
       </c>
-      <c r="I428" s="13">
+      <c r="I428" s="9">
         <v>3</v>
       </c>
-      <c r="J428" s="12" t="s">
+      <c r="J428" s="8" t="s">
         <v>973</v>
       </c>
-      <c r="K428" s="12" t="s">
+      <c r="K428" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L428" s="12" t="s">
+      <c r="L428" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="M428" s="12" t="s">
+      <c r="M428" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="N428" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="429" customHeight="1" ht="18.75">
-      <c r="A429" s="12" t="s">
+      <c r="N428" s="8"/>
+    </row>
+    <row r="429" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A429" s="8" t="s">
         <v>1435</v>
       </c>
-      <c r="B429" s="12" t="s">
+      <c r="B429" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C429" s="12" t="s">
+      <c r="C429" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D429" s="13">
-        <v>22</v>
-      </c>
-      <c r="E429" s="12" t="s">
+      <c r="D429" s="9">
+        <v>22</v>
+      </c>
+      <c r="E429" s="8" t="s">
         <v>1230</v>
       </c>
-      <c r="F429" s="12" t="s">
+      <c r="F429" s="8" t="s">
         <v>1436</v>
       </c>
-      <c r="G429" s="12" t="s">
+      <c r="G429" s="8" t="s">
         <v>1437</v>
       </c>
-      <c r="H429" s="13">
+      <c r="H429" s="9">
         <v>3</v>
       </c>
-      <c r="I429" s="13"/>
-      <c r="J429" s="12" t="s">
+      <c r="I429" s="9"/>
+      <c r="J429" s="8" t="s">
         <v>973</v>
       </c>
-      <c r="K429" s="12" t="s">
+      <c r="K429" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L429" s="12" t="s">
+      <c r="L429" s="8" t="s">
         <v>1373</v>
       </c>
-      <c r="M429" s="12" t="s">
+      <c r="M429" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="N429" s="12" t="s">
+      <c r="N429" s="8" t="s">
         <v>1398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="430" customHeight="1" ht="18.75">
-      <c r="A430" s="12"/>
-      <c r="B430" s="12"/>
-      <c r="C430" s="12"/>
-      <c r="D430" s="13"/>
-      <c r="E430" s="12"/>
-      <c r="F430" s="12"/>
-      <c r="G430" s="12"/>
-      <c r="H430" s="13"/>
-      <c r="I430" s="13"/>
-      <c r="J430" s="12"/>
-      <c r="K430" s="12"/>
-      <c r="L430" s="12"/>
-      <c r="M430" s="12"/>
-      <c r="N430" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="431" customHeight="1" ht="18.75">
-      <c r="A431" s="12"/>
-      <c r="B431" s="12"/>
-      <c r="C431" s="12"/>
-      <c r="D431" s="13"/>
-      <c r="E431" s="12"/>
-      <c r="F431" s="12"/>
-      <c r="G431" s="12"/>
-      <c r="H431" s="13"/>
-      <c r="I431" s="13"/>
-      <c r="J431" s="12"/>
-      <c r="K431" s="12"/>
-      <c r="L431" s="12"/>
-      <c r="M431" s="12"/>
-      <c r="N431" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="432" customHeight="1" ht="18.75">
-      <c r="A432" s="12" t="s">
+    <row r="430" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A430" s="8"/>
+      <c r="B430" s="8"/>
+      <c r="C430" s="8"/>
+      <c r="D430" s="9"/>
+      <c r="E430" s="8"/>
+      <c r="F430" s="8"/>
+      <c r="G430" s="8"/>
+      <c r="H430" s="9"/>
+      <c r="I430" s="9"/>
+      <c r="J430" s="8"/>
+      <c r="K430" s="8"/>
+      <c r="L430" s="8"/>
+      <c r="M430" s="8"/>
+      <c r="N430" s="8"/>
+    </row>
+    <row r="431" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A431" s="8" t="s">
         <v>1438</v>
       </c>
-      <c r="B432" s="12" t="s">
+      <c r="B431" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C432" s="12" t="s">
+      <c r="C431" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D432" s="13">
-        <v>22</v>
-      </c>
-      <c r="E432" s="12" t="s">
+      <c r="D431" s="9">
+        <v>22</v>
+      </c>
+      <c r="E431" s="8" t="s">
         <v>1439</v>
       </c>
-      <c r="F432" s="12" t="s">
+      <c r="F431" s="8" t="s">
         <v>1440</v>
       </c>
-      <c r="G432" s="12" t="s">
+      <c r="G431" s="8" t="s">
         <v>1441</v>
       </c>
-      <c r="H432" s="13"/>
-      <c r="I432" s="13"/>
-      <c r="J432" s="12"/>
-      <c r="K432" s="12"/>
-      <c r="L432" s="12"/>
-      <c r="M432" s="12"/>
-      <c r="N432" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="433" customHeight="1" ht="18.75">
-      <c r="A433" s="12" t="s">
+      <c r="H431" s="9"/>
+      <c r="I431" s="9"/>
+      <c r="J431" s="8"/>
+      <c r="K431" s="8"/>
+      <c r="L431" s="8"/>
+      <c r="M431" s="8"/>
+      <c r="N431" s="8"/>
+    </row>
+    <row r="432" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A432" s="8" t="s">
         <v>1442</v>
       </c>
-      <c r="B433" s="12" t="s">
+      <c r="B432" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C433" s="12" t="s">
+      <c r="C432" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D433" s="13">
-        <v>22</v>
-      </c>
-      <c r="E433" s="12" t="s">
+      <c r="D432" s="9">
+        <v>22</v>
+      </c>
+      <c r="E432" s="8" t="s">
         <v>1443</v>
       </c>
-      <c r="F433" s="12" t="s">
+      <c r="F432" s="8" t="s">
         <v>1440</v>
       </c>
-      <c r="G433" s="12" t="s">
+      <c r="G432" s="8" t="s">
         <v>1441</v>
       </c>
-      <c r="H433" s="13"/>
-      <c r="I433" s="13"/>
-      <c r="J433" s="12"/>
-      <c r="K433" s="12"/>
-      <c r="L433" s="12"/>
-      <c r="M433" s="12"/>
-      <c r="N433" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="434" customHeight="1" ht="18.75">
-      <c r="A434" s="12" t="s">
+      <c r="H432" s="9"/>
+      <c r="I432" s="9"/>
+      <c r="J432" s="8"/>
+      <c r="K432" s="8"/>
+      <c r="L432" s="8"/>
+      <c r="M432" s="8"/>
+      <c r="N432" s="8"/>
+    </row>
+    <row r="433" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A433" s="8" t="s">
         <v>1444</v>
       </c>
-      <c r="B434" s="12" t="s">
+      <c r="B433" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C434" s="12" t="s">
+      <c r="C433" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D434" s="13">
-        <v>22</v>
-      </c>
-      <c r="E434" s="12" t="s">
+      <c r="D433" s="9">
+        <v>22</v>
+      </c>
+      <c r="E433" s="8" t="s">
         <v>1445</v>
       </c>
-      <c r="F434" s="12" t="s">
+      <c r="F433" s="8" t="s">
         <v>1032</v>
       </c>
-      <c r="G434" s="12" t="s">
+      <c r="G433" s="8" t="s">
         <v>1446</v>
       </c>
-      <c r="H434" s="13"/>
-      <c r="I434" s="13"/>
-      <c r="J434" s="12"/>
-      <c r="K434" s="12"/>
-      <c r="L434" s="12"/>
-      <c r="M434" s="12"/>
-      <c r="N434" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="435" customHeight="1" ht="18.75">
-      <c r="A435" s="12" t="s">
+      <c r="H433" s="9"/>
+      <c r="I433" s="9"/>
+      <c r="J433" s="8"/>
+      <c r="K433" s="8"/>
+      <c r="L433" s="8"/>
+      <c r="M433" s="8"/>
+      <c r="N433" s="8"/>
+    </row>
+    <row r="434" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A434" s="8" t="s">
         <v>1447</v>
       </c>
-      <c r="B435" s="12" t="s">
+      <c r="B434" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C435" s="12" t="s">
+      <c r="C434" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D435" s="13">
-        <v>22</v>
-      </c>
-      <c r="E435" s="12" t="s">
+      <c r="D434" s="9">
+        <v>22</v>
+      </c>
+      <c r="E434" s="8" t="s">
         <v>1448</v>
       </c>
-      <c r="F435" s="12" t="s">
+      <c r="F434" s="8" t="s">
         <v>1049</v>
       </c>
-      <c r="G435" s="12" t="s">
+      <c r="G434" s="8" t="s">
         <v>1449</v>
       </c>
-      <c r="H435" s="13"/>
-      <c r="I435" s="13"/>
-      <c r="J435" s="12"/>
-      <c r="K435" s="12"/>
-      <c r="L435" s="12"/>
-      <c r="M435" s="12"/>
-      <c r="N435" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="436" customHeight="1" ht="18.75">
-      <c r="A436" s="12" t="s">
+      <c r="H434" s="9"/>
+      <c r="I434" s="9"/>
+      <c r="J434" s="8"/>
+      <c r="K434" s="8"/>
+      <c r="L434" s="8"/>
+      <c r="M434" s="8"/>
+      <c r="N434" s="8"/>
+    </row>
+    <row r="435" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A435" s="8" t="s">
         <v>1450</v>
       </c>
-      <c r="B436" s="12" t="s">
+      <c r="B435" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C436" s="12" t="s">
+      <c r="C435" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D436" s="13">
-        <v>22</v>
-      </c>
-      <c r="E436" s="12" t="s">
+      <c r="D435" s="9">
+        <v>22</v>
+      </c>
+      <c r="E435" s="8" t="s">
         <v>1021</v>
       </c>
-      <c r="F436" s="12" t="s">
+      <c r="F435" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="G436" s="12" t="s">
+      <c r="G435" s="8" t="s">
         <v>1451</v>
       </c>
-      <c r="H436" s="13"/>
-      <c r="I436" s="13"/>
-      <c r="J436" s="12"/>
-      <c r="K436" s="12"/>
-      <c r="L436" s="12"/>
-      <c r="M436" s="12"/>
-      <c r="N436" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="437" customHeight="1" ht="18.75">
-      <c r="A437" s="12" t="s">
+      <c r="H435" s="9"/>
+      <c r="I435" s="9"/>
+      <c r="J435" s="8"/>
+      <c r="K435" s="8"/>
+      <c r="L435" s="8"/>
+      <c r="M435" s="8"/>
+      <c r="N435" s="8"/>
+    </row>
+    <row r="436" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A436" s="8" t="s">
         <v>1452</v>
       </c>
-      <c r="B437" s="12" t="s">
+      <c r="B436" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C437" s="12" t="s">
+      <c r="C436" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D437" s="13">
-        <v>22</v>
-      </c>
-      <c r="E437" s="12" t="s">
+      <c r="D436" s="9">
+        <v>22</v>
+      </c>
+      <c r="E436" s="8" t="s">
         <v>1443</v>
       </c>
-      <c r="F437" s="12" t="s">
+      <c r="F436" s="8" t="s">
         <v>1044</v>
       </c>
-      <c r="G437" s="12" t="s">
+      <c r="G436" s="8" t="s">
         <v>1043</v>
       </c>
-      <c r="H437" s="13"/>
-      <c r="I437" s="13"/>
-      <c r="J437" s="12"/>
-      <c r="K437" s="12"/>
-      <c r="L437" s="12"/>
-      <c r="M437" s="12"/>
-      <c r="N437" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="438" customHeight="1" ht="18.75">
-      <c r="A438" s="12" t="s">
+      <c r="H436" s="9"/>
+      <c r="I436" s="9"/>
+      <c r="J436" s="8"/>
+      <c r="K436" s="8"/>
+      <c r="L436" s="8"/>
+      <c r="M436" s="8"/>
+      <c r="N436" s="8"/>
+    </row>
+    <row r="437" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A437" s="8" t="s">
         <v>1453</v>
       </c>
-      <c r="B438" s="12" t="s">
+      <c r="B437" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C438" s="12" t="s">
+      <c r="C437" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D438" s="13">
-        <v>22</v>
-      </c>
-      <c r="E438" s="12" t="s">
+      <c r="D437" s="9">
+        <v>22</v>
+      </c>
+      <c r="E437" s="8" t="s">
         <v>1454</v>
       </c>
-      <c r="F438" s="12" t="s">
+      <c r="F437" s="8" t="s">
         <v>1075</v>
       </c>
-      <c r="G438" s="12" t="s">
+      <c r="G437" s="8" t="s">
         <v>1072</v>
       </c>
-      <c r="H438" s="13"/>
-      <c r="I438" s="13"/>
-      <c r="J438" s="12"/>
-      <c r="K438" s="12"/>
-      <c r="L438" s="12"/>
-      <c r="M438" s="12"/>
-      <c r="N438" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="439" customHeight="1" ht="18.75">
-      <c r="A439" s="12" t="s">
+      <c r="H437" s="9"/>
+      <c r="I437" s="9"/>
+      <c r="J437" s="8"/>
+      <c r="K437" s="8"/>
+      <c r="L437" s="8"/>
+      <c r="M437" s="8"/>
+      <c r="N437" s="8"/>
+    </row>
+    <row r="438" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A438" s="8" t="s">
         <v>1455</v>
       </c>
-      <c r="B439" s="12" t="s">
+      <c r="B438" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C439" s="12" t="s">
+      <c r="C438" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D439" s="13">
-        <v>22</v>
-      </c>
-      <c r="E439" s="12" t="s">
+      <c r="D438" s="9">
+        <v>22</v>
+      </c>
+      <c r="E438" s="8" t="s">
         <v>1075</v>
       </c>
-      <c r="F439" s="12" t="s">
+      <c r="F438" s="8" t="s">
         <v>1072</v>
       </c>
-      <c r="G439" s="12" t="s">
+      <c r="G438" s="8" t="s">
         <v>1346</v>
       </c>
-      <c r="H439" s="13"/>
-      <c r="I439" s="13"/>
-      <c r="J439" s="12"/>
-      <c r="K439" s="12"/>
-      <c r="L439" s="12"/>
-      <c r="M439" s="12"/>
-      <c r="N439" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="440" customHeight="1" ht="18.75">
-      <c r="A440" s="12" t="s">
+      <c r="H438" s="9"/>
+      <c r="I438" s="9"/>
+      <c r="J438" s="8"/>
+      <c r="K438" s="8"/>
+      <c r="L438" s="8"/>
+      <c r="M438" s="8"/>
+      <c r="N438" s="8"/>
+    </row>
+    <row r="439" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A439" s="8" t="s">
         <v>1456</v>
       </c>
-      <c r="B440" s="12" t="s">
+      <c r="B439" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C440" s="12" t="s">
+      <c r="C439" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D440" s="13">
-        <v>22</v>
-      </c>
-      <c r="E440" s="12" t="s">
+      <c r="D439" s="9">
+        <v>22</v>
+      </c>
+      <c r="E439" s="8" t="s">
         <v>1078</v>
       </c>
-      <c r="F440" s="12" t="s">
+      <c r="F439" s="8" t="s">
         <v>1024</v>
       </c>
-      <c r="G440" s="12" t="s">
+      <c r="G439" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="H440" s="13"/>
-      <c r="I440" s="13"/>
-      <c r="J440" s="12"/>
-      <c r="K440" s="12"/>
-      <c r="L440" s="12"/>
-      <c r="M440" s="12"/>
-      <c r="N440" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="441" customHeight="1" ht="18.75">
-      <c r="A441" s="12" t="s">
+      <c r="H439" s="9"/>
+      <c r="I439" s="9"/>
+      <c r="J439" s="8"/>
+      <c r="K439" s="8"/>
+      <c r="L439" s="8"/>
+      <c r="M439" s="8"/>
+      <c r="N439" s="8"/>
+    </row>
+    <row r="440" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A440" s="8" t="s">
         <v>1457</v>
       </c>
-      <c r="B441" s="12" t="s">
+      <c r="B440" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C441" s="12" t="s">
+      <c r="C440" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D441" s="13">
-        <v>22</v>
-      </c>
-      <c r="E441" s="12" t="s">
+      <c r="D440" s="9">
+        <v>22</v>
+      </c>
+      <c r="E440" s="8" t="s">
         <v>1439</v>
       </c>
-      <c r="F441" s="12" t="s">
+      <c r="F440" s="8" t="s">
         <v>1045</v>
       </c>
-      <c r="G441" s="12" t="s">
+      <c r="G440" s="8" t="s">
         <v>1045</v>
       </c>
-      <c r="H441" s="13"/>
-      <c r="I441" s="13"/>
-      <c r="J441" s="12"/>
-      <c r="K441" s="12"/>
-      <c r="L441" s="12"/>
-      <c r="M441" s="12"/>
-      <c r="N441" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="442" customHeight="1" ht="18.75">
-      <c r="A442" s="12" t="s">
+      <c r="H440" s="9"/>
+      <c r="I440" s="9"/>
+      <c r="J440" s="8"/>
+      <c r="K440" s="8"/>
+      <c r="L440" s="8"/>
+      <c r="M440" s="8"/>
+      <c r="N440" s="8"/>
+    </row>
+    <row r="441" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A441" s="8" t="s">
         <v>1458</v>
       </c>
-      <c r="B442" s="12" t="s">
+      <c r="B441" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C442" s="12" t="s">
+      <c r="C441" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D442" s="13">
-        <v>22</v>
-      </c>
-      <c r="E442" s="12" t="s">
+      <c r="D441" s="9">
+        <v>22</v>
+      </c>
+      <c r="E441" s="8" t="s">
         <v>1459</v>
       </c>
-      <c r="F442" s="12" t="s">
+      <c r="F441" s="8" t="s">
         <v>1460</v>
       </c>
-      <c r="G442" s="12" t="s">
+      <c r="G441" s="8" t="s">
         <v>856</v>
       </c>
-      <c r="H442" s="13"/>
-      <c r="I442" s="13"/>
-      <c r="J442" s="12"/>
-      <c r="K442" s="12"/>
-      <c r="L442" s="12"/>
-      <c r="M442" s="12"/>
-      <c r="N442" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="443" customHeight="1" ht="18.75">
-      <c r="A443" s="12" t="s">
+      <c r="H441" s="9"/>
+      <c r="I441" s="9"/>
+      <c r="J441" s="8"/>
+      <c r="K441" s="8"/>
+      <c r="L441" s="8"/>
+      <c r="M441" s="8"/>
+      <c r="N441" s="8"/>
+    </row>
+    <row r="442" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A442" s="8" t="s">
         <v>1461</v>
       </c>
-      <c r="B443" s="12" t="s">
+      <c r="B442" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C443" s="12" t="s">
+      <c r="C442" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D443" s="13">
-        <v>22</v>
-      </c>
-      <c r="E443" s="12" t="s">
+      <c r="D442" s="9">
+        <v>22</v>
+      </c>
+      <c r="E442" s="8" t="s">
         <v>1439</v>
       </c>
-      <c r="F443" s="12" t="s">
+      <c r="F442" s="8" t="s">
         <v>1462</v>
       </c>
-      <c r="G443" s="12" t="s">
+      <c r="G442" s="8" t="s">
         <v>1454</v>
       </c>
-      <c r="H443" s="13"/>
-      <c r="I443" s="13"/>
-      <c r="J443" s="12"/>
-      <c r="K443" s="12"/>
-      <c r="L443" s="12"/>
-      <c r="M443" s="12"/>
-      <c r="N443" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="444" customHeight="1" ht="18.75">
-      <c r="A444" s="12" t="s">
+      <c r="H442" s="9"/>
+      <c r="I442" s="9"/>
+      <c r="J442" s="8"/>
+      <c r="K442" s="8"/>
+      <c r="L442" s="8"/>
+      <c r="M442" s="8"/>
+      <c r="N442" s="8"/>
+    </row>
+    <row r="443" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A443" s="8" t="s">
         <v>1463</v>
       </c>
-      <c r="B444" s="12" t="s">
+      <c r="B443" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C444" s="12" t="s">
+      <c r="C443" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D444" s="13">
-        <v>22</v>
-      </c>
-      <c r="E444" s="12" t="s">
+      <c r="D443" s="9">
+        <v>22</v>
+      </c>
+      <c r="E443" s="8" t="s">
         <v>1464</v>
       </c>
-      <c r="F444" s="12" t="s">
+      <c r="F443" s="8" t="s">
         <v>1465</v>
       </c>
-      <c r="G444" s="12" t="s">
+      <c r="G443" s="8" t="s">
         <v>1466</v>
       </c>
-      <c r="H444" s="13"/>
-      <c r="I444" s="13"/>
-      <c r="J444" s="12"/>
-      <c r="K444" s="12"/>
-      <c r="L444" s="12"/>
-      <c r="M444" s="12"/>
-      <c r="N444" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="445" customHeight="1" ht="18.75">
-      <c r="A445" s="12" t="s">
+      <c r="H443" s="9"/>
+      <c r="I443" s="9"/>
+      <c r="J443" s="8"/>
+      <c r="K443" s="8"/>
+      <c r="L443" s="8"/>
+      <c r="M443" s="8"/>
+      <c r="N443" s="8"/>
+    </row>
+    <row r="444" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A444" s="8" t="s">
         <v>1467</v>
       </c>
-      <c r="B445" s="12" t="s">
+      <c r="B444" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C445" s="12" t="s">
+      <c r="C444" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D445" s="13">
-        <v>22</v>
-      </c>
-      <c r="E445" s="12" t="s">
+      <c r="D444" s="9">
+        <v>22</v>
+      </c>
+      <c r="E444" s="8" t="s">
         <v>890</v>
       </c>
-      <c r="F445" s="12" t="s">
+      <c r="F444" s="8" t="s">
         <v>1468</v>
       </c>
-      <c r="G445" s="12" t="s">
+      <c r="G444" s="8" t="s">
         <v>1061</v>
       </c>
-      <c r="H445" s="13"/>
-      <c r="I445" s="13"/>
-      <c r="J445" s="12"/>
-      <c r="K445" s="12"/>
-      <c r="L445" s="12"/>
-      <c r="M445" s="12"/>
-      <c r="N445" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="446" customHeight="1" ht="18.75">
-      <c r="A446" s="12" t="s">
+      <c r="H444" s="9"/>
+      <c r="I444" s="9"/>
+      <c r="J444" s="8"/>
+      <c r="K444" s="8"/>
+      <c r="L444" s="8"/>
+      <c r="M444" s="8"/>
+      <c r="N444" s="8"/>
+    </row>
+    <row r="445" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A445" s="8" t="s">
         <v>1469</v>
       </c>
-      <c r="B446" s="12" t="s">
+      <c r="B445" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C446" s="12" t="s">
+      <c r="C445" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D446" s="13">
-        <v>22</v>
-      </c>
-      <c r="E446" s="12" t="s">
+      <c r="D445" s="9">
+        <v>22</v>
+      </c>
+      <c r="E445" s="8" t="s">
         <v>1470</v>
       </c>
-      <c r="F446" s="12" t="s">
+      <c r="F445" s="8" t="s">
         <v>1471</v>
       </c>
-      <c r="G446" s="12" t="s">
+      <c r="G445" s="8" t="s">
         <v>1472</v>
       </c>
-      <c r="H446" s="13"/>
-      <c r="I446" s="13"/>
-      <c r="J446" s="12"/>
-      <c r="K446" s="12"/>
-      <c r="L446" s="12"/>
-      <c r="M446" s="12"/>
-      <c r="N446" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="447" customHeight="1" ht="18.75">
-      <c r="A447" s="12" t="s">
+      <c r="H445" s="9"/>
+      <c r="I445" s="9"/>
+      <c r="J445" s="8"/>
+      <c r="K445" s="8"/>
+      <c r="L445" s="8"/>
+      <c r="M445" s="8"/>
+      <c r="N445" s="8"/>
+    </row>
+    <row r="446" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A446" s="8" t="s">
         <v>1473</v>
       </c>
-      <c r="B447" s="12" t="s">
+      <c r="B446" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C447" s="12" t="s">
+      <c r="C446" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D447" s="13">
-        <v>22</v>
-      </c>
-      <c r="E447" s="12" t="s">
+      <c r="D446" s="9">
+        <v>22</v>
+      </c>
+      <c r="E446" s="8" t="s">
         <v>1471</v>
       </c>
-      <c r="F447" s="12" t="s">
+      <c r="F446" s="8" t="s">
         <v>1472</v>
       </c>
-      <c r="G447" s="12" t="s">
+      <c r="G446" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="H447" s="13"/>
-      <c r="I447" s="13"/>
-      <c r="J447" s="12"/>
-      <c r="K447" s="12"/>
-      <c r="L447" s="12"/>
-      <c r="M447" s="12"/>
-      <c r="N447" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="448" customHeight="1" ht="18.75">
-      <c r="A448" s="12" t="s">
+      <c r="H446" s="9"/>
+      <c r="I446" s="9"/>
+      <c r="J446" s="8"/>
+      <c r="K446" s="8"/>
+      <c r="L446" s="8"/>
+      <c r="M446" s="8"/>
+      <c r="N446" s="8"/>
+    </row>
+    <row r="447" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A447" s="8" t="s">
         <v>1474</v>
       </c>
-      <c r="B448" s="12" t="s">
+      <c r="B447" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C448" s="12" t="s">
+      <c r="C447" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D448" s="13">
-        <v>22</v>
-      </c>
-      <c r="E448" s="12" t="s">
+      <c r="D447" s="9">
+        <v>22</v>
+      </c>
+      <c r="E447" s="8" t="s">
         <v>825</v>
       </c>
-      <c r="F448" s="12" t="s">
+      <c r="F447" s="8" t="s">
         <v>1475</v>
       </c>
-      <c r="G448" s="12" t="s">
+      <c r="G447" s="8" t="s">
         <v>857</v>
       </c>
-      <c r="H448" s="13"/>
-      <c r="I448" s="13"/>
-      <c r="J448" s="12"/>
-      <c r="K448" s="12"/>
-      <c r="L448" s="12"/>
-      <c r="M448" s="12"/>
-      <c r="N448" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="449" customHeight="1" ht="18.75">
-      <c r="A449" s="12" t="s">
+      <c r="H447" s="9"/>
+      <c r="I447" s="9"/>
+      <c r="J447" s="8"/>
+      <c r="K447" s="8"/>
+      <c r="L447" s="8"/>
+      <c r="M447" s="8"/>
+      <c r="N447" s="8"/>
+    </row>
+    <row r="448" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A448" s="8" t="s">
         <v>1476</v>
       </c>
-      <c r="B449" s="12" t="s">
+      <c r="B448" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C449" s="12" t="s">
+      <c r="C448" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D449" s="13">
-        <v>22</v>
-      </c>
-      <c r="E449" s="12" t="s">
+      <c r="D448" s="9">
+        <v>22</v>
+      </c>
+      <c r="E448" s="8" t="s">
         <v>1464</v>
       </c>
-      <c r="F449" s="12" t="s">
+      <c r="F448" s="8" t="s">
         <v>1471</v>
       </c>
-      <c r="G449" s="12" t="s">
+      <c r="G448" s="8" t="s">
         <v>1475</v>
       </c>
-      <c r="H449" s="13"/>
-      <c r="I449" s="13"/>
-      <c r="J449" s="12"/>
-      <c r="K449" s="12"/>
-      <c r="L449" s="12"/>
-      <c r="M449" s="12"/>
-      <c r="N449" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="450" customHeight="1" ht="18.75">
-      <c r="A450" s="12" t="s">
+      <c r="H448" s="9"/>
+      <c r="I448" s="9"/>
+      <c r="J448" s="8"/>
+      <c r="K448" s="8"/>
+      <c r="L448" s="8"/>
+      <c r="M448" s="8"/>
+      <c r="N448" s="8"/>
+    </row>
+    <row r="449" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A449" s="8" t="s">
         <v>1477</v>
       </c>
-      <c r="B450" s="12" t="s">
+      <c r="B449" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C450" s="12" t="s">
+      <c r="C449" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D450" s="13">
-        <v>22</v>
-      </c>
-      <c r="E450" s="12" t="s">
+      <c r="D449" s="9">
+        <v>22</v>
+      </c>
+      <c r="E449" s="8" t="s">
         <v>1465</v>
       </c>
-      <c r="F450" s="12" t="s">
+      <c r="F449" s="8" t="s">
         <v>1471</v>
       </c>
-      <c r="G450" s="12" t="s">
+      <c r="G449" s="8" t="s">
         <v>1475</v>
       </c>
-      <c r="H450" s="13"/>
-      <c r="I450" s="13"/>
-      <c r="J450" s="12"/>
-      <c r="K450" s="12"/>
-      <c r="L450" s="12"/>
-      <c r="M450" s="12"/>
-      <c r="N450" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="451" customHeight="1" ht="18.75">
-      <c r="A451" s="12" t="s">
+      <c r="H449" s="9"/>
+      <c r="I449" s="9"/>
+      <c r="J449" s="8"/>
+      <c r="K449" s="8"/>
+      <c r="L449" s="8"/>
+      <c r="M449" s="8"/>
+      <c r="N449" s="8"/>
+    </row>
+    <row r="450" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A450" s="8" t="s">
         <v>1478</v>
       </c>
-      <c r="B451" s="12" t="s">
+      <c r="B450" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C451" s="12" t="s">
+      <c r="C450" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D451" s="13">
-        <v>22</v>
-      </c>
-      <c r="E451" s="12" t="s">
+      <c r="D450" s="9">
+        <v>22</v>
+      </c>
+      <c r="E450" s="8" t="s">
         <v>857</v>
       </c>
-      <c r="F451" s="12" t="s">
+      <c r="F450" s="8" t="s">
         <v>857</v>
       </c>
-      <c r="G451" s="12" t="s">
+      <c r="G450" s="8" t="s">
         <v>1479</v>
       </c>
-      <c r="H451" s="13"/>
-      <c r="I451" s="13"/>
-      <c r="J451" s="12"/>
-      <c r="K451" s="12"/>
-      <c r="L451" s="12"/>
-      <c r="M451" s="12"/>
-      <c r="N451" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="452" customHeight="1" ht="18.75">
-      <c r="A452" s="12" t="s">
+      <c r="H450" s="9"/>
+      <c r="I450" s="9"/>
+      <c r="J450" s="8"/>
+      <c r="K450" s="8"/>
+      <c r="L450" s="8"/>
+      <c r="M450" s="8"/>
+      <c r="N450" s="8"/>
+    </row>
+    <row r="451" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A451" s="8" t="s">
         <v>1480</v>
       </c>
-      <c r="B452" s="12" t="s">
+      <c r="B451" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C452" s="12" t="s">
+      <c r="C451" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D452" s="13">
-        <v>22</v>
-      </c>
-      <c r="E452" s="12" t="s">
+      <c r="D451" s="9">
+        <v>22</v>
+      </c>
+      <c r="E451" s="8" t="s">
         <v>890</v>
       </c>
-      <c r="F452" s="12" t="s">
+      <c r="F451" s="8" t="s">
         <v>881</v>
       </c>
-      <c r="G452" s="12" t="s">
+      <c r="G451" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="H452" s="13"/>
-      <c r="I452" s="13"/>
-      <c r="J452" s="12"/>
-      <c r="K452" s="12"/>
-      <c r="L452" s="12"/>
-      <c r="M452" s="12"/>
-      <c r="N452" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="453" customHeight="1" ht="18.75">
-      <c r="A453" s="12"/>
-      <c r="B453" s="12"/>
-      <c r="C453" s="12"/>
-      <c r="D453" s="13"/>
-      <c r="E453" s="12"/>
-      <c r="F453" s="12"/>
-      <c r="G453" s="12"/>
-      <c r="H453" s="13"/>
-      <c r="I453" s="13"/>
-      <c r="J453" s="12"/>
-      <c r="K453" s="12"/>
-      <c r="L453" s="12"/>
-      <c r="M453" s="12"/>
-      <c r="N453" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="454" customHeight="1" ht="18.75">
-      <c r="A454" s="12" t="s">
+      <c r="H451" s="9"/>
+      <c r="I451" s="9"/>
+      <c r="J451" s="8"/>
+      <c r="K451" s="8"/>
+      <c r="L451" s="8"/>
+      <c r="M451" s="8"/>
+      <c r="N451" s="8"/>
+    </row>
+    <row r="452" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A452" s="8"/>
+      <c r="B452" s="8"/>
+      <c r="C452" s="8"/>
+      <c r="D452" s="9"/>
+      <c r="E452" s="8"/>
+      <c r="F452" s="8"/>
+      <c r="G452" s="8"/>
+      <c r="H452" s="9"/>
+      <c r="I452" s="9"/>
+      <c r="J452" s="8"/>
+      <c r="K452" s="8"/>
+      <c r="L452" s="8"/>
+      <c r="M452" s="8"/>
+      <c r="N452" s="8"/>
+    </row>
+    <row r="453" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A453" s="8" t="s">
         <v>1481</v>
       </c>
-      <c r="B454" s="12" t="s">
+      <c r="B453" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C454" s="12" t="s">
+      <c r="C453" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D454" s="13">
-        <v>22</v>
-      </c>
-      <c r="E454" s="12" t="s">
+      <c r="D453" s="9">
+        <v>22</v>
+      </c>
+      <c r="E453" s="8" t="s">
         <v>939</v>
       </c>
-      <c r="F454" s="12" t="s">
+      <c r="F453" s="8" t="s">
         <v>825</v>
       </c>
-      <c r="G454" s="12" t="s">
+      <c r="G453" s="8" t="s">
         <v>1482</v>
       </c>
-      <c r="H454" s="13">
+      <c r="H453" s="9">
         <v>4</v>
       </c>
-      <c r="I454" s="13"/>
-      <c r="J454" s="12" t="s">
+      <c r="I453" s="9"/>
+      <c r="J453" s="8" t="s">
         <v>1483</v>
       </c>
-      <c r="K454" s="12" t="s">
+      <c r="K453" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L454" s="12" t="s">
+      <c r="L453" s="8" t="s">
         <v>1368</v>
       </c>
-      <c r="M454" s="12" t="s">
+      <c r="M453" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="N454" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="455" customHeight="1" ht="18.75">
-      <c r="A455" s="12" t="s">
+      <c r="N453" s="8"/>
+    </row>
+    <row r="454" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A454" s="8" t="s">
         <v>1484</v>
       </c>
-      <c r="B455" s="12" t="s">
+      <c r="B454" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C455" s="12" t="s">
+      <c r="C454" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D455" s="13">
-        <v>22</v>
-      </c>
-      <c r="E455" s="12" t="s">
+      <c r="D454" s="9">
+        <v>22</v>
+      </c>
+      <c r="E454" s="8" t="s">
         <v>812</v>
       </c>
-      <c r="F455" s="12" t="s">
+      <c r="F454" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="G455" s="12" t="s">
+      <c r="G454" s="8" t="s">
         <v>1485</v>
       </c>
-      <c r="H455" s="13">
+      <c r="H454" s="9">
         <v>3</v>
       </c>
-      <c r="I455" s="13"/>
-      <c r="J455" s="12" t="s">
+      <c r="I454" s="9"/>
+      <c r="J454" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="K455" s="12" t="s">
+      <c r="K454" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L455" s="12" t="s">
+      <c r="L454" s="8" t="s">
         <v>1359</v>
       </c>
-      <c r="M455" s="12" t="s">
+      <c r="M454" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="N455" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="456" customHeight="1" ht="18.75">
-      <c r="A456" s="12" t="s">
+      <c r="N454" s="8"/>
+    </row>
+    <row r="455" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A455" s="8" t="s">
         <v>1486</v>
       </c>
-      <c r="B456" s="12" t="s">
+      <c r="B455" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C456" s="12" t="s">
+      <c r="C455" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D456" s="13">
-        <v>22</v>
-      </c>
-      <c r="E456" s="12" t="s">
+      <c r="D455" s="9">
+        <v>22</v>
+      </c>
+      <c r="E455" s="8" t="s">
         <v>812</v>
       </c>
-      <c r="F456" s="12" t="s">
+      <c r="F455" s="8" t="s">
         <v>1487</v>
       </c>
-      <c r="G456" s="12" t="s">
+      <c r="G455" s="8" t="s">
         <v>1488</v>
       </c>
-      <c r="H456" s="13">
+      <c r="H455" s="9">
         <v>4</v>
       </c>
-      <c r="I456" s="13"/>
-      <c r="J456" s="12" t="s">
+      <c r="I455" s="9"/>
+      <c r="J455" s="8" t="s">
         <v>937</v>
       </c>
-      <c r="K456" s="12" t="s">
+      <c r="K455" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L456" s="12" t="s">
+      <c r="L455" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="M456" s="12" t="s">
+      <c r="M455" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="N456" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="457" customHeight="1" ht="18.75">
-      <c r="A457" s="12" t="s">
+      <c r="N455" s="8"/>
+    </row>
+    <row r="456" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A456" s="8" t="s">
         <v>1489</v>
       </c>
-      <c r="B457" s="12" t="s">
+      <c r="B456" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C457" s="12" t="s">
+      <c r="C456" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D457" s="13">
-        <v>22</v>
-      </c>
-      <c r="E457" s="12" t="s">
+      <c r="D456" s="9">
+        <v>22</v>
+      </c>
+      <c r="E456" s="8" t="s">
         <v>1490</v>
       </c>
-      <c r="F457" s="12" t="s">
+      <c r="F456" s="8" t="s">
         <v>1491</v>
       </c>
-      <c r="G457" s="12" t="s">
+      <c r="G456" s="8" t="s">
         <v>1492</v>
       </c>
-      <c r="H457" s="13">
+      <c r="H456" s="9">
         <v>5</v>
       </c>
-      <c r="I457" s="13"/>
-      <c r="J457" s="12" t="s">
+      <c r="I456" s="9"/>
+      <c r="J456" s="8" t="s">
         <v>1493</v>
       </c>
-      <c r="K457" s="12" t="s">
+      <c r="K456" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L457" s="12" t="s">
+      <c r="L456" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="M457" s="12" t="s">
+      <c r="M456" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="N457" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="458" customHeight="1" ht="18.75">
-      <c r="A458" s="12" t="s">
+      <c r="N456" s="8"/>
+    </row>
+    <row r="457" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A457" s="8" t="s">
         <v>1494</v>
       </c>
-      <c r="B458" s="12" t="s">
+      <c r="B457" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C458" s="12" t="s">
+      <c r="C457" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D458" s="13">
-        <v>22</v>
-      </c>
-      <c r="E458" s="12" t="s">
+      <c r="D457" s="9">
+        <v>22</v>
+      </c>
+      <c r="E457" s="8" t="s">
         <v>1495</v>
       </c>
-      <c r="F458" s="12" t="s">
+      <c r="F457" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="G458" s="12" t="s">
+      <c r="G457" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="H458" s="13">
+      <c r="H457" s="9">
         <v>5</v>
       </c>
-      <c r="I458" s="13"/>
-      <c r="J458" s="12" t="s">
+      <c r="I457" s="9"/>
+      <c r="J457" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="K458" s="12" t="s">
+      <c r="K457" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L458" s="12" t="s">
+      <c r="L457" s="8" t="s">
         <v>1368</v>
       </c>
-      <c r="M458" s="12" t="s">
+      <c r="M457" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="N458" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="459" customHeight="1" ht="18.75">
-      <c r="A459" s="12" t="s">
+      <c r="N457" s="8"/>
+    </row>
+    <row r="458" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A458" s="8" t="s">
         <v>1496</v>
       </c>
-      <c r="B459" s="12" t="s">
+      <c r="B458" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C459" s="12" t="s">
+      <c r="C458" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D459" s="13">
-        <v>22</v>
-      </c>
-      <c r="E459" s="12" t="s">
+      <c r="D458" s="9">
+        <v>22</v>
+      </c>
+      <c r="E458" s="8" t="s">
         <v>1497</v>
       </c>
-      <c r="F459" s="12" t="s">
+      <c r="F458" s="8" t="s">
         <v>1498</v>
       </c>
-      <c r="G459" s="12" t="s">
+      <c r="G458" s="8" t="s">
         <v>1407</v>
       </c>
-      <c r="H459" s="13">
+      <c r="H458" s="9">
         <v>4</v>
       </c>
-      <c r="I459" s="13"/>
-      <c r="J459" s="12" t="s">
+      <c r="I458" s="9"/>
+      <c r="J458" s="8" t="s">
         <v>1483</v>
       </c>
-      <c r="K459" s="12" t="s">
+      <c r="K458" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L459" s="12" t="s">
+      <c r="L458" s="8" t="s">
         <v>1373</v>
       </c>
-      <c r="M459" s="12" t="s">
+      <c r="M458" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="N459" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="460" customHeight="1" ht="18.75">
-      <c r="A460" s="12" t="s">
+      <c r="N458" s="8"/>
+    </row>
+    <row r="459" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A459" s="8" t="s">
         <v>1499</v>
       </c>
-      <c r="B460" s="12" t="s">
+      <c r="B459" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C460" s="12" t="s">
+      <c r="C459" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D460" s="13">
-        <v>22</v>
-      </c>
-      <c r="E460" s="12" t="s">
+      <c r="D459" s="9">
+        <v>22</v>
+      </c>
+      <c r="E459" s="8" t="s">
         <v>1500</v>
       </c>
-      <c r="F460" s="12" t="s">
+      <c r="F459" s="8" t="s">
         <v>1501</v>
       </c>
-      <c r="G460" s="12" t="s">
+      <c r="G459" s="8" t="s">
         <v>1502</v>
       </c>
-      <c r="H460" s="13">
+      <c r="H459" s="9">
         <v>3</v>
       </c>
-      <c r="I460" s="13"/>
-      <c r="J460" s="12" t="s">
+      <c r="I459" s="9"/>
+      <c r="J459" s="8" t="s">
         <v>1483</v>
       </c>
-      <c r="K460" s="12" t="s">
+      <c r="K459" s="8" t="s">
         <v>1215</v>
       </c>
-      <c r="L460" s="12" t="s">
+      <c r="L459" s="8" t="s">
         <v>1503</v>
       </c>
-      <c r="M460" s="12" t="s">
+      <c r="M459" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="N460" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="461" customHeight="1" ht="18.75">
-      <c r="A461" s="12" t="s">
+      <c r="N459" s="8"/>
+    </row>
+    <row r="460" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A460" s="8" t="s">
         <v>1504</v>
       </c>
-      <c r="B461" s="12" t="s">
+      <c r="B460" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C461" s="12" t="s">
+      <c r="C460" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D461" s="13">
-        <v>22</v>
-      </c>
-      <c r="E461" s="12" t="s">
+      <c r="D460" s="9">
+        <v>22</v>
+      </c>
+      <c r="E460" s="8" t="s">
         <v>1505</v>
       </c>
-      <c r="F461" s="12" t="s">
+      <c r="F460" s="8" t="s">
         <v>1506</v>
       </c>
-      <c r="G461" s="12" t="s">
+      <c r="G460" s="8" t="s">
         <v>1507</v>
       </c>
-      <c r="H461" s="13">
+      <c r="H460" s="9">
         <v>3</v>
       </c>
-      <c r="I461" s="13">
+      <c r="I460" s="9">
         <v>5</v>
       </c>
-      <c r="J461" s="12" t="s">
+      <c r="J460" s="8" t="s">
         <v>973</v>
       </c>
-      <c r="K461" s="12" t="s">
+      <c r="K460" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L461" s="12" t="s">
+      <c r="L460" s="8" t="s">
         <v>1508</v>
       </c>
-      <c r="M461" s="12" t="s">
+      <c r="M460" s="8" t="s">
         <v>1509</v>
       </c>
-      <c r="N461" s="12" t="s">
+      <c r="N460" s="8" t="s">
         <v>1398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="462" customHeight="1" ht="18.75">
-      <c r="A462" s="12" t="s">
+    <row r="461" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A461" s="8" t="s">
         <v>1510</v>
       </c>
-      <c r="B462" s="12" t="s">
+      <c r="B461" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C462" s="12" t="s">
+      <c r="C461" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D462" s="13">
-        <v>22</v>
-      </c>
-      <c r="E462" s="12" t="s">
+      <c r="D461" s="9">
+        <v>22</v>
+      </c>
+      <c r="E461" s="8" t="s">
         <v>568</v>
       </c>
-      <c r="F462" s="12" t="s">
+      <c r="F461" s="8" t="s">
         <v>1511</v>
       </c>
-      <c r="G462" s="12" t="s">
+      <c r="G461" s="8" t="s">
         <v>1512</v>
       </c>
-      <c r="H462" s="13">
+      <c r="H461" s="9">
         <v>4</v>
       </c>
-      <c r="I462" s="13"/>
-      <c r="J462" s="12" t="s">
+      <c r="I461" s="9"/>
+      <c r="J461" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="K462" s="12" t="s">
+      <c r="K461" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L462" s="12" t="s">
+      <c r="L461" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="M462" s="12" t="s">
+      <c r="M461" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="N462" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="463" customHeight="1" ht="18.75">
-      <c r="A463" s="12" t="s">
+      <c r="N461" s="8"/>
+    </row>
+    <row r="462" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A462" s="8" t="s">
         <v>1513</v>
       </c>
-      <c r="B463" s="12" t="s">
+      <c r="B462" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C463" s="12" t="s">
+      <c r="C462" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D463" s="13">
-        <v>22</v>
-      </c>
-      <c r="E463" s="12" t="s">
+      <c r="D462" s="9">
+        <v>22</v>
+      </c>
+      <c r="E462" s="8" t="s">
         <v>1514</v>
       </c>
-      <c r="F463" s="12" t="s">
+      <c r="F462" s="8" t="s">
         <v>1515</v>
       </c>
-      <c r="G463" s="12" t="s">
+      <c r="G462" s="8" t="s">
         <v>1371</v>
       </c>
-      <c r="H463" s="13">
+      <c r="H462" s="9">
         <v>3</v>
       </c>
-      <c r="I463" s="13">
+      <c r="I462" s="9">
         <v>5</v>
       </c>
-      <c r="J463" s="12" t="s">
+      <c r="J462" s="8" t="s">
         <v>1516</v>
       </c>
-      <c r="K463" s="12" t="s">
+      <c r="K462" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L463" s="12" t="s">
+      <c r="L462" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="M463" s="12" t="s">
+      <c r="M462" s="8" t="s">
         <v>1517</v>
       </c>
-      <c r="N463" s="12" t="s">
+      <c r="N462" s="8" t="s">
         <v>1398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="464" customHeight="1" ht="18.75">
-      <c r="A464" s="12" t="s">
+    <row r="463" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A463" s="8" t="s">
         <v>1518</v>
       </c>
-      <c r="B464" s="12" t="s">
+      <c r="B463" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C464" s="12" t="s">
+      <c r="C463" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D464" s="13">
-        <v>22</v>
-      </c>
-      <c r="E464" s="12" t="s">
+      <c r="D463" s="9">
+        <v>22</v>
+      </c>
+      <c r="E463" s="8" t="s">
         <v>1506</v>
       </c>
-      <c r="F464" s="12" t="s">
+      <c r="F463" s="8" t="s">
         <v>1519</v>
       </c>
-      <c r="G464" s="12" t="s">
+      <c r="G463" s="8" t="s">
         <v>1520</v>
       </c>
-      <c r="H464" s="13">
+      <c r="H463" s="9">
         <v>3</v>
       </c>
-      <c r="I464" s="13">
+      <c r="I463" s="9">
         <v>3</v>
       </c>
-      <c r="J464" s="12" t="s">
+      <c r="J463" s="8" t="s">
         <v>1103</v>
       </c>
-      <c r="K464" s="12" t="s">
+      <c r="K463" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L464" s="12" t="s">
+      <c r="L463" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="M464" s="12" t="s">
+      <c r="M463" s="8" t="s">
         <v>1521</v>
       </c>
-      <c r="N464" s="12" t="s">
+      <c r="N463" s="8" t="s">
         <v>1398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="465" customHeight="1" ht="18.75">
-      <c r="A465" s="12" t="s">
+    <row r="464" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A464" s="8" t="s">
         <v>1522</v>
       </c>
-      <c r="B465" s="12" t="s">
+      <c r="B464" s="8" t="s">
         <v>1387</v>
       </c>
-      <c r="C465" s="12" t="s">
+      <c r="C464" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D465" s="13">
-        <v>22</v>
-      </c>
-      <c r="E465" s="12" t="s">
+      <c r="D464" s="9">
+        <v>22</v>
+      </c>
+      <c r="E464" s="8" t="s">
         <v>1523</v>
       </c>
-      <c r="F465" s="12" t="s">
+      <c r="F464" s="8" t="s">
         <v>1524</v>
       </c>
-      <c r="G465" s="12" t="s">
+      <c r="G464" s="8" t="s">
         <v>1426</v>
       </c>
-      <c r="H465" s="13">
+      <c r="H464" s="9">
         <v>3</v>
       </c>
-      <c r="I465" s="13"/>
-      <c r="J465" s="12" t="s">
+      <c r="I464" s="9"/>
+      <c r="J464" s="8" t="s">
         <v>1103</v>
       </c>
-      <c r="K465" s="12" t="s">
+      <c r="K464" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L465" s="12" t="s">
+      <c r="L464" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="M465" s="12" t="s">
+      <c r="M464" s="8" t="s">
         <v>1521</v>
       </c>
-      <c r="N465" s="12" t="s">
+      <c r="N464" s="8" t="s">
         <v>1398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="466" customHeight="1" ht="18.75">
-      <c r="A466" s="12"/>
-      <c r="B466" s="12"/>
-      <c r="C466" s="12"/>
-      <c r="D466" s="13"/>
-      <c r="E466" s="12"/>
-      <c r="F466" s="12"/>
-      <c r="G466" s="12"/>
-      <c r="H466" s="13"/>
-      <c r="I466" s="13"/>
-      <c r="J466" s="12"/>
-      <c r="K466" s="12"/>
-      <c r="L466" s="12"/>
-      <c r="M466" s="12"/>
-      <c r="N466" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="467" customHeight="1" ht="18.75">
-      <c r="A467" s="12" t="s">
+    <row r="465" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A465" s="8"/>
+      <c r="B465" s="8"/>
+      <c r="C465" s="8"/>
+      <c r="D465" s="9"/>
+      <c r="E465" s="8"/>
+      <c r="F465" s="8"/>
+      <c r="G465" s="8"/>
+      <c r="H465" s="9"/>
+      <c r="I465" s="9"/>
+      <c r="J465" s="8"/>
+      <c r="K465" s="8"/>
+      <c r="L465" s="8"/>
+      <c r="M465" s="8"/>
+      <c r="N465" s="8"/>
+    </row>
+    <row r="466" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A466" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="B467" s="12" t="s">
+      <c r="B466" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C467" s="12" t="s">
+      <c r="C466" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D467" s="13">
-        <v>22</v>
-      </c>
-      <c r="E467" s="12" t="s">
+      <c r="D466" s="9">
+        <v>22</v>
+      </c>
+      <c r="E466" s="8" t="s">
         <v>606</v>
       </c>
-      <c r="F467" s="12" t="s">
+      <c r="F466" s="8" t="s">
         <v>1527</v>
       </c>
-      <c r="G467" s="12" t="s">
+      <c r="G466" s="8" t="s">
         <v>1207</v>
       </c>
-      <c r="H467" s="13">
+      <c r="H466" s="9">
         <v>3</v>
       </c>
-      <c r="I467" s="13">
+      <c r="I466" s="9">
         <v>4</v>
       </c>
-      <c r="J467" s="12" t="s">
+      <c r="J466" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K467" s="12" t="s">
+      <c r="K466" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L467" s="12" t="s">
+      <c r="L466" s="8" t="s">
         <v>848</v>
       </c>
-      <c r="M467" s="12" t="s">
+      <c r="M466" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N467" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="468" customHeight="1" ht="18.75">
-      <c r="A468" s="12" t="s">
+      <c r="N466" s="8"/>
+    </row>
+    <row r="467" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A467" s="8" t="s">
         <v>1529</v>
       </c>
-      <c r="B468" s="12" t="s">
+      <c r="B467" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C468" s="12" t="s">
+      <c r="C467" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D468" s="13">
-        <v>22</v>
-      </c>
-      <c r="E468" s="12" t="s">
+      <c r="D467" s="9">
+        <v>22</v>
+      </c>
+      <c r="E467" s="8" t="s">
         <v>1530</v>
       </c>
-      <c r="F468" s="12" t="s">
+      <c r="F467" s="8" t="s">
         <v>1531</v>
       </c>
-      <c r="G468" s="12" t="s">
+      <c r="G467" s="8" t="s">
         <v>1532</v>
       </c>
-      <c r="H468" s="13">
+      <c r="H467" s="9">
         <v>3</v>
       </c>
-      <c r="I468" s="13">
+      <c r="I467" s="9">
         <v>2</v>
       </c>
-      <c r="J468" s="12" t="s">
+      <c r="J467" s="8" t="s">
         <v>1533</v>
       </c>
-      <c r="K468" s="12" t="s">
+      <c r="K467" s="8" t="s">
         <v>1215</v>
       </c>
-      <c r="L468" s="12" t="s">
+      <c r="L467" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M468" s="12" t="s">
+      <c r="M467" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N468" s="12" t="s">
+      <c r="N467" s="8" t="s">
         <v>1534</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="469" customHeight="1" ht="18.75">
-      <c r="A469" s="12" t="s">
+    <row r="468" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A468" s="8" t="s">
         <v>1535</v>
       </c>
-      <c r="B469" s="12" t="s">
+      <c r="B468" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C469" s="12" t="s">
+      <c r="C468" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D469" s="13">
-        <v>22</v>
-      </c>
-      <c r="E469" s="12" t="s">
+      <c r="D468" s="9">
+        <v>22</v>
+      </c>
+      <c r="E468" s="8" t="s">
         <v>1536</v>
       </c>
-      <c r="F469" s="12" t="s">
+      <c r="F468" s="8" t="s">
         <v>1393</v>
       </c>
-      <c r="G469" s="12" t="s">
+      <c r="G468" s="8" t="s">
         <v>1241</v>
       </c>
-      <c r="H469" s="13">
+      <c r="H468" s="9">
         <v>3</v>
       </c>
-      <c r="I469" s="13">
+      <c r="I468" s="9">
         <v>4</v>
       </c>
-      <c r="J469" s="12" t="s">
+      <c r="J468" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K469" s="12" t="s">
+      <c r="K468" s="8" t="s">
         <v>1215</v>
       </c>
-      <c r="L469" s="12" t="s">
+      <c r="L468" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M469" s="12" t="s">
+      <c r="M468" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N469" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="470" customHeight="1" ht="18.75">
-      <c r="A470" s="12" t="s">
+      <c r="N468" s="8"/>
+    </row>
+    <row r="469" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A469" s="8" t="s">
         <v>1537</v>
       </c>
-      <c r="B470" s="12" t="s">
+      <c r="B469" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C470" s="12" t="s">
+      <c r="C469" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D470" s="13">
-        <v>22</v>
-      </c>
-      <c r="E470" s="12" t="s">
+      <c r="D469" s="9">
+        <v>22</v>
+      </c>
+      <c r="E469" s="8" t="s">
         <v>1538</v>
       </c>
-      <c r="F470" s="12" t="s">
+      <c r="F469" s="8" t="s">
         <v>1539</v>
       </c>
-      <c r="G470" s="12" t="s">
+      <c r="G469" s="8" t="s">
         <v>1540</v>
       </c>
-      <c r="H470" s="13">
+      <c r="H469" s="9">
         <v>3</v>
       </c>
-      <c r="I470" s="13">
+      <c r="I469" s="9">
         <v>3</v>
       </c>
-      <c r="J470" s="12" t="s">
+      <c r="J469" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K470" s="12" t="s">
+      <c r="K469" s="8" t="s">
         <v>1215</v>
       </c>
-      <c r="L470" s="12" t="s">
+      <c r="L469" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M470" s="12" t="s">
+      <c r="M469" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N470" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="471" customHeight="1" ht="18.75">
-      <c r="A471" s="12" t="s">
+      <c r="N469" s="8"/>
+    </row>
+    <row r="470" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A470" s="8" t="s">
         <v>1541</v>
       </c>
-      <c r="B471" s="12" t="s">
+      <c r="B470" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C471" s="12" t="s">
+      <c r="C470" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D471" s="13">
-        <v>22</v>
-      </c>
-      <c r="E471" s="12" t="s">
+      <c r="D470" s="9">
+        <v>22</v>
+      </c>
+      <c r="E470" s="8" t="s">
         <v>1542</v>
       </c>
-      <c r="F471" s="12" t="s">
+      <c r="F470" s="8" t="s">
         <v>1543</v>
       </c>
-      <c r="G471" s="12" t="s">
+      <c r="G470" s="8" t="s">
         <v>1430</v>
       </c>
-      <c r="H471" s="13">
+      <c r="H470" s="9">
         <v>3</v>
       </c>
-      <c r="I471" s="13">
+      <c r="I470" s="9">
         <v>3</v>
       </c>
-      <c r="J471" s="12" t="s">
+      <c r="J470" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="K471" s="12" t="s">
+      <c r="K470" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L471" s="12" t="s">
+      <c r="L470" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="M471" s="12" t="s">
+      <c r="M470" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N471" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="472" customHeight="1" ht="18.75">
-      <c r="A472" s="12" t="s">
+      <c r="N470" s="8"/>
+    </row>
+    <row r="471" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A471" s="8" t="s">
         <v>1544</v>
       </c>
-      <c r="B472" s="12" t="s">
+      <c r="B471" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C472" s="12" t="s">
+      <c r="C471" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D472" s="13">
-        <v>22</v>
-      </c>
-      <c r="E472" s="12" t="s">
+      <c r="D471" s="9">
+        <v>22</v>
+      </c>
+      <c r="E471" s="8" t="s">
         <v>1545</v>
       </c>
-      <c r="F472" s="12" t="s">
+      <c r="F471" s="8" t="s">
         <v>802</v>
       </c>
-      <c r="G472" s="12" t="s">
+      <c r="G471" s="8" t="s">
         <v>1546</v>
       </c>
-      <c r="H472" s="13">
+      <c r="H471" s="9">
         <v>3</v>
       </c>
-      <c r="I472" s="13">
+      <c r="I471" s="9">
         <v>3</v>
       </c>
-      <c r="J472" s="12" t="s">
+      <c r="J471" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K472" s="12" t="s">
+      <c r="K471" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L472" s="12" t="s">
+      <c r="L471" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M472" s="12" t="s">
+      <c r="M471" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N472" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="473" customHeight="1" ht="18.75">
-      <c r="A473" s="12" t="s">
+      <c r="N471" s="8"/>
+    </row>
+    <row r="472" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A472" s="8" t="s">
         <v>1547</v>
       </c>
-      <c r="B473" s="12" t="s">
+      <c r="B472" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C473" s="12" t="s">
+      <c r="C472" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D473" s="13">
-        <v>22</v>
-      </c>
-      <c r="E473" s="12" t="s">
+      <c r="D472" s="9">
+        <v>22</v>
+      </c>
+      <c r="E472" s="8" t="s">
         <v>1548</v>
       </c>
-      <c r="F473" s="12" t="s">
+      <c r="F472" s="8" t="s">
         <v>1241</v>
       </c>
-      <c r="G473" s="12" t="s">
+      <c r="G472" s="8" t="s">
         <v>1549</v>
       </c>
-      <c r="H473" s="13">
+      <c r="H472" s="9">
         <v>4</v>
       </c>
-      <c r="I473" s="13">
+      <c r="I472" s="9">
         <v>2</v>
       </c>
-      <c r="J473" s="12" t="s">
+      <c r="J472" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="K473" s="12" t="s">
+      <c r="K472" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L473" s="12" t="s">
+      <c r="L472" s="8" t="s">
         <v>1508</v>
       </c>
-      <c r="M473" s="12" t="s">
+      <c r="M472" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N473" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="474" customHeight="1" ht="18.75">
-      <c r="A474" s="12" t="s">
+      <c r="N472" s="8"/>
+    </row>
+    <row r="473" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A473" s="8" t="s">
         <v>1550</v>
       </c>
-      <c r="B474" s="12" t="s">
+      <c r="B473" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C474" s="12" t="s">
+      <c r="C473" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D474" s="13">
-        <v>22</v>
-      </c>
-      <c r="E474" s="12" t="s">
+      <c r="D473" s="9">
+        <v>22</v>
+      </c>
+      <c r="E473" s="8" t="s">
         <v>1551</v>
       </c>
-      <c r="F474" s="12" t="s">
+      <c r="F473" s="8" t="s">
         <v>1552</v>
       </c>
-      <c r="G474" s="12" t="s">
+      <c r="G473" s="8" t="s">
         <v>1123</v>
       </c>
-      <c r="H474" s="13">
+      <c r="H473" s="9">
         <v>3</v>
       </c>
-      <c r="I474" s="13">
+      <c r="I473" s="9">
         <v>2</v>
       </c>
-      <c r="J474" s="12" t="s">
+      <c r="J473" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K474" s="12" t="s">
+      <c r="K473" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L474" s="12" t="s">
+      <c r="L473" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M474" s="12" t="s">
+      <c r="M473" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N474" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="475" customHeight="1" ht="18.75">
-      <c r="A475" s="12" t="s">
+      <c r="N473" s="8"/>
+    </row>
+    <row r="474" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A474" s="8" t="s">
         <v>1553</v>
       </c>
-      <c r="B475" s="12" t="s">
+      <c r="B474" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C475" s="12" t="s">
+      <c r="C474" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D475" s="13">
-        <v>22</v>
-      </c>
-      <c r="E475" s="12" t="s">
+      <c r="D474" s="9">
+        <v>22</v>
+      </c>
+      <c r="E474" s="8" t="s">
         <v>1548</v>
       </c>
-      <c r="F475" s="12" t="s">
+      <c r="F474" s="8" t="s">
         <v>1554</v>
       </c>
-      <c r="G475" s="12" t="s">
+      <c r="G474" s="8" t="s">
         <v>1555</v>
       </c>
-      <c r="H475" s="13">
+      <c r="H474" s="9">
         <v>3</v>
       </c>
-      <c r="I475" s="13">
+      <c r="I474" s="9">
         <v>2</v>
       </c>
-      <c r="J475" s="12" t="s">
+      <c r="J474" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="K475" s="12" t="s">
+      <c r="K474" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L475" s="12" t="s">
+      <c r="L474" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M475" s="12" t="s">
+      <c r="M474" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N475" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="476" customHeight="1" ht="18.75">
-      <c r="A476" s="12" t="s">
+      <c r="N474" s="8"/>
+    </row>
+    <row r="475" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A475" s="8" t="s">
         <v>1556</v>
       </c>
-      <c r="B476" s="12" t="s">
+      <c r="B475" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C476" s="12" t="s">
+      <c r="C475" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D476" s="13">
-        <v>22</v>
-      </c>
-      <c r="E476" s="12" t="s">
+      <c r="D475" s="9">
+        <v>22</v>
+      </c>
+      <c r="E475" s="8" t="s">
         <v>1557</v>
       </c>
-      <c r="F476" s="12" t="s">
+      <c r="F475" s="8" t="s">
         <v>1230</v>
       </c>
-      <c r="G476" s="12" t="s">
+      <c r="G475" s="8" t="s">
         <v>1558</v>
       </c>
-      <c r="H476" s="13">
+      <c r="H475" s="9">
         <v>4</v>
       </c>
-      <c r="I476" s="13"/>
-      <c r="J476" s="12" t="s">
+      <c r="I475" s="9"/>
+      <c r="J475" s="8" t="s">
         <v>969</v>
       </c>
-      <c r="K476" s="12" t="s">
+      <c r="K475" s="8" t="s">
         <v>1215</v>
       </c>
-      <c r="L476" s="12" t="s">
+      <c r="L475" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="M476" s="12" t="s">
+      <c r="M475" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N476" s="12" t="s">
+      <c r="N475" s="8" t="s">
         <v>1534</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="477" customHeight="1" ht="18.75">
-      <c r="A477" s="12" t="s">
+    <row r="476" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A476" s="8" t="s">
         <v>1559</v>
       </c>
-      <c r="B477" s="12" t="s">
+      <c r="B476" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C477" s="12" t="s">
+      <c r="C476" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D477" s="13">
-        <v>22</v>
-      </c>
-      <c r="E477" s="12" t="s">
+      <c r="D476" s="9">
+        <v>22</v>
+      </c>
+      <c r="E476" s="8" t="s">
         <v>1560</v>
       </c>
-      <c r="F477" s="12" t="s">
+      <c r="F476" s="8" t="s">
         <v>1561</v>
       </c>
-      <c r="G477" s="12" t="s">
+      <c r="G476" s="8" t="s">
         <v>1167</v>
       </c>
-      <c r="H477" s="13">
+      <c r="H476" s="9">
         <v>3</v>
       </c>
-      <c r="I477" s="13"/>
-      <c r="J477" s="12" t="s">
+      <c r="I476" s="9"/>
+      <c r="J476" s="8" t="s">
         <v>1562</v>
       </c>
-      <c r="K477" s="12" t="s">
+      <c r="K476" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L477" s="12" t="s">
+      <c r="L476" s="8" t="s">
         <v>565</v>
       </c>
-      <c r="M477" s="12" t="s">
+      <c r="M476" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N477" s="12" t="s">
+      <c r="N476" s="8" t="s">
         <v>1534</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="478" customHeight="1" ht="18.75">
-      <c r="A478" s="12" t="s">
+    <row r="477" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A477" s="8" t="s">
         <v>1563</v>
       </c>
-      <c r="B478" s="12" t="s">
+      <c r="B477" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C478" s="12" t="s">
+      <c r="C477" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D478" s="13">
-        <v>22</v>
-      </c>
-      <c r="E478" s="12" t="s">
+      <c r="D477" s="9">
+        <v>22</v>
+      </c>
+      <c r="E477" s="8" t="s">
         <v>567</v>
       </c>
-      <c r="F478" s="12" t="s">
+      <c r="F477" s="8" t="s">
         <v>1524</v>
       </c>
-      <c r="G478" s="12" t="s">
+      <c r="G477" s="8" t="s">
         <v>1564</v>
       </c>
-      <c r="H478" s="13">
+      <c r="H477" s="9">
         <v>3</v>
       </c>
-      <c r="I478" s="13">
+      <c r="I477" s="9">
         <v>2</v>
       </c>
-      <c r="J478" s="12" t="s">
+      <c r="J477" s="8" t="s">
         <v>791</v>
       </c>
-      <c r="K478" s="12" t="s">
+      <c r="K477" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L478" s="12" t="s">
+      <c r="L477" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M478" s="12" t="s">
+      <c r="M477" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N478" s="12" t="s">
+      <c r="N477" s="8" t="s">
         <v>1534</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="479" customHeight="1" ht="18.75">
-      <c r="A479" s="12" t="s">
+    <row r="478" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A478" s="8" t="s">
         <v>1565</v>
       </c>
-      <c r="B479" s="12" t="s">
+      <c r="B478" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C479" s="12" t="s">
+      <c r="C478" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D479" s="13">
-        <v>22</v>
-      </c>
-      <c r="E479" s="12" t="s">
+      <c r="D478" s="9">
+        <v>22</v>
+      </c>
+      <c r="E478" s="8" t="s">
         <v>1566</v>
       </c>
-      <c r="F479" s="12" t="s">
+      <c r="F478" s="8" t="s">
         <v>1567</v>
       </c>
-      <c r="G479" s="12" t="s">
+      <c r="G478" s="8" t="s">
         <v>1568</v>
       </c>
-      <c r="H479" s="13">
+      <c r="H478" s="9">
         <v>4</v>
       </c>
-      <c r="I479" s="13"/>
-      <c r="J479" s="12" t="s">
+      <c r="I478" s="9"/>
+      <c r="J478" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="K479" s="12" t="s">
+      <c r="K478" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="L479" s="12" t="s">
+      <c r="L478" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M479" s="12" t="s">
+      <c r="M478" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N479" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="480" customHeight="1" ht="18.75">
-      <c r="A480" s="12" t="s">
+      <c r="N478" s="8"/>
+    </row>
+    <row r="479" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A479" s="8" t="s">
         <v>1569</v>
       </c>
-      <c r="B480" s="12" t="s">
+      <c r="B479" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C480" s="12" t="s">
+      <c r="C479" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D480" s="13">
-        <v>22</v>
-      </c>
-      <c r="E480" s="12" t="s">
+      <c r="D479" s="9">
+        <v>22</v>
+      </c>
+      <c r="E479" s="8" t="s">
         <v>1570</v>
       </c>
-      <c r="F480" s="12" t="s">
+      <c r="F479" s="8" t="s">
         <v>1571</v>
       </c>
-      <c r="G480" s="12" t="s">
+      <c r="G479" s="8" t="s">
         <v>1371</v>
       </c>
-      <c r="H480" s="13">
+      <c r="H479" s="9">
         <v>3</v>
       </c>
-      <c r="I480" s="13"/>
-      <c r="J480" s="12" t="s">
+      <c r="I479" s="9"/>
+      <c r="J479" s="8" t="s">
         <v>1483</v>
       </c>
-      <c r="K480" s="12" t="s">
+      <c r="K479" s="8" t="s">
         <v>1215</v>
       </c>
-      <c r="L480" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="M480" s="12" t="s">
+      <c r="L479" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M479" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N480" s="12" t="s">
+      <c r="N479" s="8" t="s">
         <v>1534</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="481" customHeight="1" ht="18.75">
-      <c r="A481" s="12" t="s">
+    <row r="480" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A480" s="8" t="s">
         <v>1572</v>
       </c>
-      <c r="B481" s="12" t="s">
+      <c r="B480" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C481" s="12" t="s">
+      <c r="C480" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D481" s="13">
-        <v>22</v>
-      </c>
-      <c r="E481" s="12" t="s">
+      <c r="D480" s="9">
+        <v>22</v>
+      </c>
+      <c r="E480" s="8" t="s">
         <v>1573</v>
       </c>
-      <c r="F481" s="12" t="s">
+      <c r="F480" s="8" t="s">
         <v>1241</v>
       </c>
-      <c r="G481" s="12" t="s">
+      <c r="G480" s="8" t="s">
         <v>1574</v>
       </c>
-      <c r="H481" s="13">
+      <c r="H480" s="9">
         <v>3</v>
       </c>
-      <c r="I481" s="13">
+      <c r="I480" s="9">
         <v>3</v>
       </c>
-      <c r="J481" s="12" t="s">
+      <c r="J480" s="8" t="s">
         <v>791</v>
       </c>
-      <c r="K481" s="12" t="s">
+      <c r="K480" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L481" s="12" t="s">
+      <c r="L480" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M481" s="12" t="s">
+      <c r="M480" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N481" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="482" customHeight="1" ht="18.75">
-      <c r="A482" s="12" t="s">
+      <c r="N480" s="8"/>
+    </row>
+    <row r="481" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A481" s="8" t="s">
         <v>1575</v>
       </c>
-      <c r="B482" s="12" t="s">
+      <c r="B481" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C482" s="12" t="s">
+      <c r="C481" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D482" s="13">
-        <v>22</v>
-      </c>
-      <c r="E482" s="12" t="s">
+      <c r="D481" s="9">
+        <v>22</v>
+      </c>
+      <c r="E481" s="8" t="s">
         <v>1218</v>
       </c>
-      <c r="F482" s="12" t="s">
+      <c r="F481" s="8" t="s">
         <v>1576</v>
       </c>
-      <c r="G482" s="12" t="s">
+      <c r="G481" s="8" t="s">
         <v>1577</v>
       </c>
-      <c r="H482" s="13">
+      <c r="H481" s="9">
         <v>3</v>
       </c>
-      <c r="I482" s="13"/>
-      <c r="J482" s="12" t="s">
+      <c r="I481" s="9"/>
+      <c r="J481" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K482" s="12" t="s">
+      <c r="K481" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L482" s="12" t="s">
+      <c r="L481" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="M482" s="12" t="s">
+      <c r="M481" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N482" s="12" t="s">
+      <c r="N481" s="8" t="s">
         <v>1534</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="483" customHeight="1" ht="18.75">
-      <c r="A483" s="12"/>
-      <c r="B483" s="12"/>
-      <c r="C483" s="12"/>
-      <c r="D483" s="13"/>
-      <c r="E483" s="12"/>
-      <c r="F483" s="12"/>
-      <c r="G483" s="12"/>
-      <c r="H483" s="13"/>
-      <c r="I483" s="13"/>
-      <c r="J483" s="12"/>
-      <c r="K483" s="12"/>
-      <c r="L483" s="12"/>
-      <c r="M483" s="12"/>
-      <c r="N483" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="484" customHeight="1" ht="18.75">
-      <c r="A484" s="12" t="s">
+    <row r="482" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A482" s="8" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B482" s="8" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C482" s="8" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D482" s="9">
+        <v>22</v>
+      </c>
+      <c r="E482" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="F482" s="8" t="s">
+        <v>1608</v>
+      </c>
+      <c r="G482" s="8" t="s">
+        <v>939</v>
+      </c>
+      <c r="H482" s="9">
+        <v>3</v>
+      </c>
+      <c r="I482" s="9"/>
+      <c r="J482" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="K482" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="L482" s="8" t="s">
+        <v>1373</v>
+      </c>
+      <c r="M482" s="8" t="s">
+        <v>1528</v>
+      </c>
+      <c r="N482" s="8" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="483" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A483" s="8"/>
+      <c r="B483" s="8"/>
+      <c r="C483" s="8"/>
+      <c r="D483" s="9"/>
+      <c r="E483" s="8"/>
+      <c r="F483" s="8"/>
+      <c r="G483" s="8"/>
+      <c r="H483" s="9"/>
+      <c r="I483" s="9"/>
+      <c r="J483" s="8"/>
+      <c r="K483" s="8"/>
+      <c r="L483" s="8"/>
+      <c r="M483" s="8"/>
+      <c r="N483" s="8"/>
+    </row>
+    <row r="484" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A484" s="8" t="s">
         <v>1578</v>
       </c>
-      <c r="B484" s="12" t="s">
+      <c r="B484" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C484" s="12" t="s">
+      <c r="C484" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D484" s="13">
-        <v>22</v>
-      </c>
-      <c r="E484" s="12" t="s">
+      <c r="D484" s="9">
+        <v>22</v>
+      </c>
+      <c r="E484" s="8" t="s">
         <v>1045</v>
       </c>
-      <c r="F484" s="12" t="s">
+      <c r="F484" s="8" t="s">
         <v>696</v>
       </c>
-      <c r="G484" s="12" t="s">
+      <c r="G484" s="8" t="s">
         <v>856</v>
       </c>
-      <c r="H484" s="13"/>
-      <c r="I484" s="13"/>
-      <c r="J484" s="12"/>
-      <c r="K484" s="12"/>
-      <c r="L484" s="12"/>
-      <c r="M484" s="12"/>
-      <c r="N484" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="485" customHeight="1" ht="18.75">
-      <c r="A485" s="12" t="s">
+      <c r="H484" s="9"/>
+      <c r="I484" s="9"/>
+      <c r="J484" s="8"/>
+      <c r="K484" s="8"/>
+      <c r="L484" s="8"/>
+      <c r="M484" s="8"/>
+      <c r="N484" s="8"/>
+    </row>
+    <row r="485" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A485" s="8" t="s">
         <v>1579</v>
       </c>
-      <c r="B485" s="12" t="s">
+      <c r="B485" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C485" s="12" t="s">
+      <c r="C485" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D485" s="13">
-        <v>22</v>
-      </c>
-      <c r="E485" s="12" t="s">
+      <c r="D485" s="9">
+        <v>22</v>
+      </c>
+      <c r="E485" s="8" t="s">
         <v>1032</v>
       </c>
-      <c r="F485" s="12" t="s">
+      <c r="F485" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="G485" s="12" t="s">
+      <c r="G485" s="8" t="s">
         <v>1580</v>
       </c>
-      <c r="H485" s="13"/>
-      <c r="I485" s="13"/>
-      <c r="J485" s="12"/>
-      <c r="K485" s="12"/>
-      <c r="L485" s="12"/>
-      <c r="M485" s="12"/>
-      <c r="N485" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="486" customHeight="1" ht="18.75">
-      <c r="A486" s="12" t="s">
+      <c r="H485" s="9"/>
+      <c r="I485" s="9"/>
+      <c r="J485" s="8"/>
+      <c r="K485" s="8"/>
+      <c r="L485" s="8"/>
+      <c r="M485" s="8"/>
+      <c r="N485" s="8"/>
+    </row>
+    <row r="486" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A486" s="8" t="s">
         <v>1581</v>
       </c>
-      <c r="B486" s="12" t="s">
+      <c r="B486" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C486" s="12" t="s">
+      <c r="C486" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D486" s="13">
-        <v>22</v>
-      </c>
-      <c r="E486" s="12" t="s">
+      <c r="D486" s="9">
+        <v>22</v>
+      </c>
+      <c r="E486" s="8" t="s">
         <v>1032</v>
       </c>
-      <c r="F486" s="12" t="s">
+      <c r="F486" s="8" t="s">
         <v>856</v>
       </c>
-      <c r="G486" s="12" t="s">
+      <c r="G486" s="8" t="s">
         <v>1043</v>
       </c>
-      <c r="H486" s="13"/>
-      <c r="I486" s="13"/>
-      <c r="J486" s="12"/>
-      <c r="K486" s="12"/>
-      <c r="L486" s="12"/>
-      <c r="M486" s="12"/>
-      <c r="N486" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="487" customHeight="1" ht="18.75">
-      <c r="A487" s="12" t="s">
+      <c r="H486" s="9"/>
+      <c r="I486" s="9"/>
+      <c r="J486" s="8"/>
+      <c r="K486" s="8"/>
+      <c r="L486" s="8"/>
+      <c r="M486" s="8"/>
+      <c r="N486" s="8"/>
+    </row>
+    <row r="487" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A487" s="8" t="s">
         <v>1582</v>
       </c>
-      <c r="B487" s="12" t="s">
+      <c r="B487" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C487" s="12" t="s">
+      <c r="C487" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D487" s="13">
-        <v>22</v>
-      </c>
-      <c r="E487" s="12" t="s">
+      <c r="D487" s="9">
+        <v>22</v>
+      </c>
+      <c r="E487" s="8" t="s">
         <v>1583</v>
       </c>
-      <c r="F487" s="12" t="s">
+      <c r="F487" s="8" t="s">
         <v>856</v>
       </c>
-      <c r="G487" s="12" t="s">
+      <c r="G487" s="8" t="s">
         <v>1584</v>
       </c>
-      <c r="H487" s="13"/>
-      <c r="I487" s="13"/>
-      <c r="J487" s="12"/>
-      <c r="K487" s="12"/>
-      <c r="L487" s="12"/>
-      <c r="M487" s="12"/>
-      <c r="N487" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="488" customHeight="1" ht="18.75">
-      <c r="A488" s="12" t="s">
+      <c r="H487" s="9"/>
+      <c r="I487" s="9"/>
+      <c r="J487" s="8"/>
+      <c r="K487" s="8"/>
+      <c r="L487" s="8"/>
+      <c r="M487" s="8"/>
+      <c r="N487" s="8"/>
+    </row>
+    <row r="488" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A488" s="8" t="s">
         <v>1585</v>
       </c>
-      <c r="B488" s="12" t="s">
+      <c r="B488" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C488" s="12" t="s">
+      <c r="C488" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D488" s="13">
-        <v>22</v>
-      </c>
-      <c r="E488" s="12" t="s">
+      <c r="D488" s="9">
+        <v>22</v>
+      </c>
+      <c r="E488" s="8" t="s">
         <v>1586</v>
       </c>
-      <c r="F488" s="12" t="s">
+      <c r="F488" s="8" t="s">
         <v>1587</v>
       </c>
-      <c r="G488" s="12" t="s">
+      <c r="G488" s="8" t="s">
         <v>1588</v>
       </c>
-      <c r="H488" s="13"/>
-      <c r="I488" s="13"/>
-      <c r="J488" s="12"/>
-      <c r="K488" s="12"/>
-      <c r="L488" s="12"/>
-      <c r="M488" s="12"/>
-      <c r="N488" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="489" customHeight="1" ht="18.75">
-      <c r="A489" s="12" t="s">
+      <c r="H488" s="9"/>
+      <c r="I488" s="9"/>
+      <c r="J488" s="8"/>
+      <c r="K488" s="8"/>
+      <c r="L488" s="8"/>
+      <c r="M488" s="8"/>
+      <c r="N488" s="8"/>
+    </row>
+    <row r="489" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A489" s="8" t="s">
         <v>1589</v>
       </c>
-      <c r="B489" s="12" t="s">
+      <c r="B489" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C489" s="12" t="s">
+      <c r="C489" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D489" s="13">
-        <v>22</v>
-      </c>
-      <c r="E489" s="12" t="s">
+      <c r="D489" s="9">
+        <v>22</v>
+      </c>
+      <c r="E489" s="8" t="s">
         <v>1586</v>
       </c>
-      <c r="F489" s="12" t="s">
+      <c r="F489" s="8" t="s">
         <v>1590</v>
       </c>
-      <c r="G489" s="12" t="s">
+      <c r="G489" s="8" t="s">
         <v>1028</v>
       </c>
-      <c r="H489" s="13"/>
-      <c r="I489" s="13"/>
-      <c r="J489" s="12"/>
-      <c r="K489" s="12"/>
-      <c r="L489" s="12"/>
-      <c r="M489" s="12"/>
-      <c r="N489" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="490" customHeight="1" ht="18.75">
-      <c r="A490" s="12" t="s">
+      <c r="H489" s="9"/>
+      <c r="I489" s="9"/>
+      <c r="J489" s="8"/>
+      <c r="K489" s="8"/>
+      <c r="L489" s="8"/>
+      <c r="M489" s="8"/>
+      <c r="N489" s="8"/>
+    </row>
+    <row r="490" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A490" s="8" t="s">
         <v>1591</v>
       </c>
-      <c r="B490" s="12" t="s">
+      <c r="B490" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C490" s="12" t="s">
+      <c r="C490" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D490" s="13">
-        <v>22</v>
-      </c>
-      <c r="E490" s="12" t="s">
+      <c r="D490" s="9">
+        <v>22</v>
+      </c>
+      <c r="E490" s="8" t="s">
         <v>1586</v>
       </c>
-      <c r="F490" s="12" t="s">
+      <c r="F490" s="8" t="s">
         <v>1592</v>
       </c>
-      <c r="G490" s="12" t="s">
+      <c r="G490" s="8" t="s">
         <v>1593</v>
       </c>
-      <c r="H490" s="13"/>
-      <c r="I490" s="13"/>
-      <c r="J490" s="12"/>
-      <c r="K490" s="12"/>
-      <c r="L490" s="12"/>
-      <c r="M490" s="12"/>
-      <c r="N490" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="491" customHeight="1" ht="18.75">
-      <c r="A491" s="12" t="s">
+      <c r="H490" s="9"/>
+      <c r="I490" s="9"/>
+      <c r="J490" s="8"/>
+      <c r="K490" s="8"/>
+      <c r="L490" s="8"/>
+      <c r="M490" s="8"/>
+      <c r="N490" s="8"/>
+    </row>
+    <row r="491" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A491" s="8" t="s">
         <v>1594</v>
       </c>
-      <c r="B491" s="12" t="s">
+      <c r="B491" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C491" s="12" t="s">
+      <c r="C491" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D491" s="13">
-        <v>22</v>
-      </c>
-      <c r="E491" s="12" t="s">
+      <c r="D491" s="9">
+        <v>22</v>
+      </c>
+      <c r="E491" s="8" t="s">
         <v>1580</v>
       </c>
-      <c r="F491" s="12" t="s">
+      <c r="F491" s="8" t="s">
         <v>1595</v>
       </c>
-      <c r="G491" s="12" t="s">
+      <c r="G491" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="H491" s="13"/>
-      <c r="I491" s="13"/>
-      <c r="J491" s="12"/>
-      <c r="K491" s="12"/>
-      <c r="L491" s="12"/>
-      <c r="M491" s="12"/>
-      <c r="N491" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="492" customHeight="1" ht="18.75">
-      <c r="A492" s="12" t="s">
+      <c r="H491" s="9"/>
+      <c r="I491" s="9"/>
+      <c r="J491" s="8"/>
+      <c r="K491" s="8"/>
+      <c r="L491" s="8"/>
+      <c r="M491" s="8"/>
+      <c r="N491" s="8"/>
+    </row>
+    <row r="492" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A492" s="8" t="s">
         <v>1596</v>
       </c>
-      <c r="B492" s="12" t="s">
+      <c r="B492" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C492" s="12" t="s">
+      <c r="C492" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D492" s="13">
-        <v>22</v>
-      </c>
-      <c r="E492" s="12" t="s">
+      <c r="D492" s="9">
+        <v>22</v>
+      </c>
+      <c r="E492" s="8" t="s">
         <v>1590</v>
       </c>
-      <c r="F492" s="12" t="s">
+      <c r="F492" s="8" t="s">
         <v>1597</v>
       </c>
-      <c r="G492" s="12" t="s">
+      <c r="G492" s="8" t="s">
         <v>856</v>
       </c>
-      <c r="H492" s="13"/>
-      <c r="I492" s="13"/>
-      <c r="J492" s="12"/>
-      <c r="K492" s="12"/>
-      <c r="L492" s="12"/>
-      <c r="M492" s="12"/>
-      <c r="N492" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="493" customHeight="1" ht="18.75">
-      <c r="A493" s="12" t="s">
+      <c r="H492" s="9"/>
+      <c r="I492" s="9"/>
+      <c r="J492" s="8"/>
+      <c r="K492" s="8"/>
+      <c r="L492" s="8"/>
+      <c r="M492" s="8"/>
+      <c r="N492" s="8"/>
+    </row>
+    <row r="493" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A493" s="8" t="s">
         <v>1598</v>
       </c>
-      <c r="B493" s="12" t="s">
+      <c r="B493" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C493" s="12" t="s">
+      <c r="C493" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D493" s="13">
-        <v>22</v>
-      </c>
-      <c r="E493" s="12" t="s">
+      <c r="D493" s="9">
+        <v>22</v>
+      </c>
+      <c r="E493" s="8" t="s">
         <v>1599</v>
       </c>
-      <c r="F493" s="12" t="s">
+      <c r="F493" s="8" t="s">
         <v>1600</v>
       </c>
-      <c r="G493" s="12" t="s">
+      <c r="G493" s="8" t="s">
         <v>1601</v>
       </c>
-      <c r="H493" s="13"/>
-      <c r="I493" s="13"/>
-      <c r="J493" s="12"/>
-      <c r="K493" s="12"/>
-      <c r="L493" s="12"/>
-      <c r="M493" s="12"/>
-      <c r="N493" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="494" customHeight="1" ht="18.75">
-      <c r="A494" s="12" t="s">
+      <c r="H493" s="9"/>
+      <c r="I493" s="9"/>
+      <c r="J493" s="8"/>
+      <c r="K493" s="8"/>
+      <c r="L493" s="8"/>
+      <c r="M493" s="8"/>
+      <c r="N493" s="8"/>
+    </row>
+    <row r="494" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A494" s="8" t="s">
         <v>1602</v>
       </c>
-      <c r="B494" s="12" t="s">
+      <c r="B494" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C494" s="12" t="s">
+      <c r="C494" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D494" s="13">
-        <v>22</v>
-      </c>
-      <c r="E494" s="12" t="s">
+      <c r="D494" s="9">
+        <v>22</v>
+      </c>
+      <c r="E494" s="8" t="s">
         <v>1075</v>
       </c>
-      <c r="F494" s="12" t="s">
+      <c r="F494" s="8" t="s">
         <v>1072</v>
       </c>
-      <c r="G494" s="12" t="s">
+      <c r="G494" s="8" t="s">
         <v>1459</v>
       </c>
-      <c r="H494" s="13"/>
-      <c r="I494" s="13"/>
-      <c r="J494" s="12"/>
-      <c r="K494" s="12"/>
-      <c r="L494" s="12"/>
-      <c r="M494" s="12"/>
-      <c r="N494" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="495" customHeight="1" ht="18.75">
-      <c r="A495" s="12"/>
-      <c r="B495" s="12"/>
-      <c r="C495" s="12"/>
-      <c r="D495" s="13"/>
-      <c r="E495" s="12"/>
-      <c r="F495" s="12"/>
-      <c r="G495" s="12"/>
-      <c r="H495" s="13"/>
-      <c r="I495" s="13"/>
-      <c r="J495" s="12"/>
-      <c r="K495" s="12"/>
-      <c r="L495" s="12"/>
-      <c r="M495" s="12"/>
-      <c r="N495" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="496" customHeight="1" ht="18.75">
-      <c r="A496" s="12" t="s">
+      <c r="H494" s="9"/>
+      <c r="I494" s="9"/>
+      <c r="J494" s="8"/>
+      <c r="K494" s="8"/>
+      <c r="L494" s="8"/>
+      <c r="M494" s="8"/>
+      <c r="N494" s="8"/>
+    </row>
+    <row r="495" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A495" s="8"/>
+      <c r="B495" s="8"/>
+      <c r="C495" s="8"/>
+      <c r="D495" s="9"/>
+      <c r="E495" s="8"/>
+      <c r="F495" s="8"/>
+      <c r="G495" s="8"/>
+      <c r="H495" s="9"/>
+      <c r="I495" s="9"/>
+      <c r="J495" s="8"/>
+      <c r="K495" s="8"/>
+      <c r="L495" s="8"/>
+      <c r="M495" s="8"/>
+      <c r="N495" s="8"/>
+    </row>
+    <row r="496" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A496" s="8" t="s">
         <v>1603</v>
       </c>
-      <c r="B496" s="12" t="s">
+      <c r="B496" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C496" s="12" t="s">
+      <c r="C496" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D496" s="13">
-        <v>22</v>
-      </c>
-      <c r="E496" s="12" t="s">
+      <c r="D496" s="9">
+        <v>22</v>
+      </c>
+      <c r="E496" s="8" t="s">
         <v>1604</v>
       </c>
-      <c r="F496" s="12" t="s">
+      <c r="F496" s="8" t="s">
         <v>1605</v>
       </c>
-      <c r="G496" s="12" t="s">
+      <c r="G496" s="8" t="s">
         <v>1606</v>
       </c>
-      <c r="H496" s="13">
+      <c r="H496" s="9">
         <v>3</v>
       </c>
-      <c r="I496" s="13"/>
-      <c r="J496" s="12" t="s">
+      <c r="I496" s="9"/>
+      <c r="J496" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="K496" s="12" t="s">
+      <c r="K496" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L496" s="12" t="s">
+      <c r="L496" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="M496" s="12" t="s">
+      <c r="M496" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="N496" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="497" customHeight="1" ht="18.75">
-      <c r="A497" s="12" t="s">
-        <v>1607</v>
-      </c>
-      <c r="B497" s="12" t="s">
+      <c r="N496" s="8"/>
+    </row>
+    <row r="497" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A497" s="8" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B497" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="C497" s="12" t="s">
+      <c r="C497" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D497" s="13">
-        <v>22</v>
-      </c>
-      <c r="E497" s="12" t="s">
+      <c r="D497" s="9">
+        <v>22</v>
+      </c>
+      <c r="E497" s="8" t="s">
+        <v>1542</v>
+      </c>
+      <c r="F497" s="8" t="s">
+        <v>1400</v>
+      </c>
+      <c r="G497" s="8" t="s">
+        <v>1527</v>
+      </c>
+      <c r="H497" s="9">
+        <v>3</v>
+      </c>
+      <c r="I497" s="9">
+        <v>3</v>
+      </c>
+      <c r="J497" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="K497" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="L497" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M497" s="8" t="s">
+        <v>1528</v>
+      </c>
+      <c r="N497" s="8"/>
+    </row>
+    <row r="498" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A498" s="8" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B498" s="8" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C498" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D498" s="9">
+        <v>22</v>
+      </c>
+      <c r="E498" s="8" t="s">
+        <v>1611</v>
+      </c>
+      <c r="F498" s="8" t="s">
+        <v>1612</v>
+      </c>
+      <c r="G498" s="8" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H498" s="9">
+        <v>3</v>
+      </c>
+      <c r="I498" s="9">
+        <v>2</v>
+      </c>
+      <c r="J498" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="K498" s="8" t="s">
+        <v>1215</v>
+      </c>
+      <c r="L498" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M498" s="8" t="s">
+        <v>1528</v>
+      </c>
+      <c r="N498" s="8" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="499" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A499" s="8" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B499" s="8" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C499" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D499" s="9">
+        <v>22</v>
+      </c>
+      <c r="E499" s="8" t="s">
+        <v>1614</v>
+      </c>
+      <c r="F499" s="8" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G499" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="H499" s="9">
+        <v>3</v>
+      </c>
+      <c r="I499" s="9">
+        <v>3</v>
+      </c>
+      <c r="J499" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="K499" s="8" t="s">
+        <v>1215</v>
+      </c>
+      <c r="L499" s="8" t="s">
+        <v>848</v>
+      </c>
+      <c r="M499" s="8" t="s">
+        <v>1528</v>
+      </c>
+      <c r="N499" s="8"/>
+    </row>
+    <row r="500" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A500" s="8" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B500" s="8" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C500" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D500" s="9">
+        <v>22</v>
+      </c>
+      <c r="E500" s="8" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F500" s="8" t="s">
+        <v>1618</v>
+      </c>
+      <c r="G500" s="8" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H500" s="9">
+        <v>3</v>
+      </c>
+      <c r="I500" s="9"/>
+      <c r="J500" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="K500" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="L500" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M500" s="8" t="s">
+        <v>1528</v>
+      </c>
+      <c r="N500" s="8"/>
+    </row>
+    <row r="501" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A501" s="8" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B501" s="8" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C501" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D501" s="9">
+        <v>22</v>
+      </c>
+      <c r="E501" s="8" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F501" s="8" t="s">
+        <v>1620</v>
+      </c>
+      <c r="G501" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="H501" s="9">
+        <v>3</v>
+      </c>
+      <c r="I501" s="9"/>
+      <c r="J501" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="K501" s="8" t="s">
+        <v>1215</v>
+      </c>
+      <c r="L501" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M501" s="8" t="s">
+        <v>1528</v>
+      </c>
+      <c r="N501" s="8"/>
+    </row>
+    <row r="502" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A502" s="8" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B502" s="8" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C502" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D502" s="9">
+        <v>22</v>
+      </c>
+      <c r="E502" s="8" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F502" s="8" t="s">
+        <v>1623</v>
+      </c>
+      <c r="G502" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="H502" s="9">
+        <v>4</v>
+      </c>
+      <c r="I502" s="9"/>
+      <c r="J502" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K502" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="L502" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="M502" s="8" t="s">
+        <v>1528</v>
+      </c>
+      <c r="N502" s="8"/>
+    </row>
+    <row r="503" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A503" s="8" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B503" s="8" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C503" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D503" s="9">
+        <v>22</v>
+      </c>
+      <c r="E503" s="8" t="s">
         <v>568</v>
       </c>
-      <c r="F497" s="12" t="s">
-        <v>1608</v>
-      </c>
-      <c r="G497" s="12" t="s">
-        <v>939</v>
-      </c>
-      <c r="H497" s="13">
-        <v>3</v>
-      </c>
-      <c r="I497" s="13"/>
-      <c r="J497" s="12" t="s">
-        <v>791</v>
-      </c>
-      <c r="K497" s="12" t="s">
+      <c r="F503" s="8" t="s">
+        <v>1625</v>
+      </c>
+      <c r="G503" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H503" s="9">
+        <v>5</v>
+      </c>
+      <c r="I503" s="9"/>
+      <c r="J503" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="K503" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="L497" s="12" t="s">
-        <v>1373</v>
-      </c>
-      <c r="M497" s="12" t="s">
+      <c r="L503" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="M503" s="8" t="s">
         <v>1528</v>
       </c>
-      <c r="N497" s="12" t="s">
-        <v>1534</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="498" customHeight="1" ht="18.75">
-      <c r="A498" s="12" t="s">
-        <v>1609</v>
-      </c>
-      <c r="B498" s="12" t="s">
-        <v>1526</v>
-      </c>
-      <c r="C498" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D498" s="13">
-        <v>22</v>
-      </c>
-      <c r="E498" s="12" t="s">
-        <v>1542</v>
-      </c>
-      <c r="F498" s="12" t="s">
-        <v>1400</v>
-      </c>
-      <c r="G498" s="12" t="s">
-        <v>1527</v>
-      </c>
-      <c r="H498" s="13">
-        <v>3</v>
-      </c>
-      <c r="I498" s="13">
-        <v>3</v>
-      </c>
-      <c r="J498" s="12" t="s">
-        <v>937</v>
-      </c>
-      <c r="K498" s="12" t="s">
-        <v>551</v>
-      </c>
-      <c r="L498" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="M498" s="12" t="s">
-        <v>1528</v>
-      </c>
-      <c r="N498" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="499" customHeight="1" ht="18.75">
-      <c r="A499" s="12" t="s">
-        <v>1610</v>
-      </c>
-      <c r="B499" s="12" t="s">
-        <v>1526</v>
-      </c>
-      <c r="C499" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D499" s="13">
-        <v>22</v>
-      </c>
-      <c r="E499" s="12" t="s">
-        <v>1611</v>
-      </c>
-      <c r="F499" s="12" t="s">
-        <v>1612</v>
-      </c>
-      <c r="G499" s="12" t="s">
-        <v>1123</v>
-      </c>
-      <c r="H499" s="13">
-        <v>3</v>
-      </c>
-      <c r="I499" s="13">
-        <v>2</v>
-      </c>
-      <c r="J499" s="12" t="s">
-        <v>791</v>
-      </c>
-      <c r="K499" s="12" t="s">
-        <v>1215</v>
-      </c>
-      <c r="L499" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="M499" s="12" t="s">
-        <v>1528</v>
-      </c>
-      <c r="N499" s="12" t="s">
-        <v>1534</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="500" customHeight="1" ht="18.75">
-      <c r="A500" s="12" t="s">
-        <v>1613</v>
-      </c>
-      <c r="B500" s="12" t="s">
-        <v>1526</v>
-      </c>
-      <c r="C500" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D500" s="13">
-        <v>22</v>
-      </c>
-      <c r="E500" s="12" t="s">
-        <v>1614</v>
-      </c>
-      <c r="F500" s="12" t="s">
-        <v>1615</v>
-      </c>
-      <c r="G500" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="H500" s="13">
-        <v>3</v>
-      </c>
-      <c r="I500" s="13">
-        <v>3</v>
-      </c>
-      <c r="J500" s="12" t="s">
-        <v>937</v>
-      </c>
-      <c r="K500" s="12" t="s">
-        <v>1215</v>
-      </c>
-      <c r="L500" s="12" t="s">
-        <v>848</v>
-      </c>
-      <c r="M500" s="12" t="s">
-        <v>1528</v>
-      </c>
-      <c r="N500" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="501" customHeight="1" ht="18.75">
-      <c r="A501" s="12" t="s">
-        <v>1616</v>
-      </c>
-      <c r="B501" s="12" t="s">
-        <v>1526</v>
-      </c>
-      <c r="C501" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D501" s="13">
-        <v>22</v>
-      </c>
-      <c r="E501" s="12" t="s">
-        <v>1617</v>
-      </c>
-      <c r="F501" s="12" t="s">
-        <v>1618</v>
-      </c>
-      <c r="G501" s="12" t="s">
-        <v>1207</v>
-      </c>
-      <c r="H501" s="13">
-        <v>3</v>
-      </c>
-      <c r="I501" s="13"/>
-      <c r="J501" s="12" t="s">
-        <v>937</v>
-      </c>
-      <c r="K501" s="12" t="s">
-        <v>551</v>
-      </c>
-      <c r="L501" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="M501" s="12" t="s">
-        <v>1528</v>
-      </c>
-      <c r="N501" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="502" customHeight="1" ht="18.75">
-      <c r="A502" s="12" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B502" s="12" t="s">
-        <v>1526</v>
-      </c>
-      <c r="C502" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D502" s="13">
-        <v>22</v>
-      </c>
-      <c r="E502" s="12" t="s">
-        <v>1554</v>
-      </c>
-      <c r="F502" s="12" t="s">
-        <v>1620</v>
-      </c>
-      <c r="G502" s="12" t="s">
-        <v>567</v>
-      </c>
-      <c r="H502" s="13">
-        <v>3</v>
-      </c>
-      <c r="I502" s="13"/>
-      <c r="J502" s="12" t="s">
-        <v>937</v>
-      </c>
-      <c r="K502" s="12" t="s">
-        <v>1215</v>
-      </c>
-      <c r="L502" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="M502" s="12" t="s">
-        <v>1528</v>
-      </c>
-      <c r="N502" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="503" customHeight="1" ht="18.75">
-      <c r="A503" s="12" t="s">
-        <v>1621</v>
-      </c>
-      <c r="B503" s="12" t="s">
-        <v>1526</v>
-      </c>
-      <c r="C503" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D503" s="13">
-        <v>22</v>
-      </c>
-      <c r="E503" s="12" t="s">
-        <v>1622</v>
-      </c>
-      <c r="F503" s="12" t="s">
-        <v>1623</v>
-      </c>
-      <c r="G503" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="H503" s="13">
-        <v>4</v>
-      </c>
-      <c r="I503" s="13"/>
-      <c r="J503" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="K503" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="L503" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="M503" s="12" t="s">
-        <v>1528</v>
-      </c>
-      <c r="N503" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="504" customHeight="1" ht="18.75">
-      <c r="A504" s="12" t="s">
-        <v>1624</v>
-      </c>
-      <c r="B504" s="12" t="s">
-        <v>1526</v>
-      </c>
-      <c r="C504" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D504" s="13">
-        <v>22</v>
-      </c>
-      <c r="E504" s="12" t="s">
-        <v>568</v>
-      </c>
-      <c r="F504" s="12" t="s">
-        <v>1625</v>
-      </c>
-      <c r="G504" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H504" s="13">
-        <v>5</v>
-      </c>
-      <c r="I504" s="13"/>
-      <c r="J504" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="K504" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="L504" s="12" t="s">
-        <v>1368</v>
-      </c>
-      <c r="M504" s="12" t="s">
-        <v>1528</v>
-      </c>
-      <c r="N504" s="12" t="s">
+      <c r="N503" s="8" t="s">
         <v>1534</v>
       </c>
     </row>
@@ -23019,6 +23021,7 @@
     <mergeCell ref="A414:B415"/>
     <mergeCell ref="D414:M414"/>
   </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>